--- a/Excel/video_durations.xlsx
+++ b/Excel/video_durations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9000"/>
+    <workbookView windowWidth="13284" windowHeight="5195"/>
   </bookViews>
   <sheets>
     <sheet name="video_durations" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="1048">
   <si>
     <t>artist</t>
   </si>
@@ -1242,10 +1242,16 @@
     <t>My Girl</t>
   </si>
   <si>
-    <t>Weeknd The</t>
-  </si>
-  <si>
-    <t>Save Your Tears</t>
+    <t>อาจจะป็นคนนี้</t>
+  </si>
+  <si>
+    <t>ขอมือเธอหน่อย</t>
+  </si>
+  <si>
+    <t>Wynners</t>
+  </si>
+  <si>
+    <t>I'll never dance again</t>
   </si>
   <si>
     <t>Yvonne Elliman</t>
@@ -1260,27 +1266,45 @@
     <t>In the year 2525</t>
   </si>
   <si>
-    <t>ACDC</t>
-  </si>
-  <si>
-    <t>Highway to Hell_ACDC .mp4</t>
+    <t>1910 Fruitgum Co</t>
+  </si>
+  <si>
+    <t>Simon Says</t>
+  </si>
+  <si>
+    <t>B. J. Thomas</t>
+  </si>
+  <si>
+    <t>Raindrops Keep Falling On My Head</t>
+  </si>
+  <si>
+    <t>Raindrops Keep Falling On My Head_B. J. Thomas.mp4</t>
+  </si>
+  <si>
+    <t>ก่อน</t>
+  </si>
+  <si>
+    <t>Cliff Richard</t>
+  </si>
+  <si>
+    <t>The Young Ones</t>
+  </si>
+  <si>
+    <t>The Young Ones_Cliff Richard.mp4</t>
+  </si>
+  <si>
+    <t>Dolly Parton</t>
+  </si>
+  <si>
+    <t>Islands in the stream</t>
+  </si>
+  <si>
+    <t>The Last Waltz</t>
   </si>
   <si>
     <t>Adele</t>
   </si>
   <si>
-    <t>Easy On Me</t>
-  </si>
-  <si>
-    <t>Easy On Me_Adele .mp4</t>
-  </si>
-  <si>
-    <t>Rolling in the Deep</t>
-  </si>
-  <si>
-    <t>Rolling in the Deep_Adele .mp4</t>
-  </si>
-  <si>
     <t>Someone Like You</t>
   </si>
   <si>
@@ -1377,15 +1401,6 @@
     <t>Complicated</t>
   </si>
   <si>
-    <t>B. J. Thomas</t>
-  </si>
-  <si>
-    <t>Raindrops Keep Falling On My Head</t>
-  </si>
-  <si>
-    <t>Raindrops Keep Falling On My Head_B. J. Thomas.mp4</t>
-  </si>
-  <si>
     <t>Backstreet Boys</t>
   </si>
   <si>
@@ -1854,9 +1869,6 @@
     <t>Where Does My Heart Beat Now_Celine Dion.mp4</t>
   </si>
   <si>
-    <t>Cliff Richard</t>
-  </si>
-  <si>
     <t>Evergreen Tree</t>
   </si>
   <si>
@@ -1869,12 +1881,6 @@
     <t>Poor Boy_Cliff Richard.mp4</t>
   </si>
   <si>
-    <t>The Young Ones</t>
-  </si>
-  <si>
-    <t>The Young Ones_Cliff Richard.mp4</t>
-  </si>
-  <si>
     <t>Clocks</t>
   </si>
   <si>
@@ -2077,12 +2083,6 @@
   </si>
   <si>
     <t>Let Me Love You</t>
-  </si>
-  <si>
-    <t>Dolly Parton</t>
-  </si>
-  <si>
-    <t>Islands in the stream</t>
   </si>
   <si>
     <t>New Rules</t>
@@ -3866,7 +3866,7 @@
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3911,6 +3911,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4250,7 +4251,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I477"/>
+  <dimension ref="A1:I483"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.4444444444444" customWidth="1"/>
@@ -8117,7 +8118,7 @@
     <row r="179" s="1" customFormat="1" ht="22.2" spans="1:5">
       <c r="A179" s="16"/>
       <c r="B179" s="17" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C179" s="25">
         <v>46291</v>
@@ -8156,7 +8157,7 @@
     <row r="181" s="1" customFormat="1" ht="22.2" spans="1:5">
       <c r="A181" s="16"/>
       <c r="B181" s="17" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C181" s="12">
         <v>46292</v>
@@ -8170,10 +8171,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B182" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C182" s="2">
         <v>46293</v>
@@ -8187,10 +8188,10 @@
     </row>
     <row r="183" customFormat="1" spans="1:5">
       <c r="A183" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C183" s="2">
         <v>46294</v>
@@ -8204,10 +8205,10 @@
     </row>
     <row r="184" customFormat="1" spans="1:5">
       <c r="A184" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C184" s="2">
         <v>46295</v>
@@ -8219,39 +8220,27 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="185" customFormat="1" spans="1:8">
+    <row r="185" customFormat="1" ht="23.4" spans="1:5">
       <c r="A185" t="s">
-        <v>385</v>
-      </c>
-      <c r="B185"/>
+        <v>387</v>
+      </c>
+      <c r="B185" s="26" t="s">
+        <v>388</v>
+      </c>
       <c r="C185" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D185" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F185" t="s">
-        <v>386</v>
-      </c>
-      <c r="G185">
-        <v>207.13</v>
-      </c>
-      <c r="H185">
-        <v>3.45216666666666</v>
-      </c>
-    </row>
-    <row r="186" customFormat="1" spans="1:8">
+        <v>46296</v>
+      </c>
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B186" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C186" s="2">
-        <v>46327</v>
+        <v>46297</v>
       </c>
       <c r="D186" t="s">
         <v>9</v>
@@ -8260,203 +8249,140 @@
         <v>46327</v>
       </c>
       <c r="F186" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G186">
-        <v>227.71</v>
+        <v>180.13</v>
       </c>
       <c r="H186">
-        <v>3.79516666666666</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8">
-      <c r="A187" t="s">
-        <v>387</v>
-      </c>
-      <c r="B187" t="s">
-        <v>390</v>
-      </c>
-      <c r="C187" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D187" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F187" t="s">
-        <v>391</v>
-      </c>
-      <c r="G187">
-        <v>234</v>
-      </c>
-      <c r="H187">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8">
+        <v>3.00216666666666</v>
+      </c>
+    </row>
+    <row r="187" s="1" customFormat="1" ht="22.2" spans="1:5">
+      <c r="A187" s="16"/>
+      <c r="B187" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="C187" s="25">
+        <v>46298</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="13">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="188" customFormat="1" hidden="1" spans="1:8">
       <c r="A188" t="s">
-        <v>387</v>
-      </c>
-      <c r="B188" t="s">
-        <v>392</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B188" s="24"/>
       <c r="C188" s="2">
-        <v>46327</v>
+        <v>46270</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
       </c>
       <c r="E188" s="3">
-        <v>46327</v>
+        <v>46270</v>
       </c>
       <c r="F188" t="s">
+        <v>339</v>
+      </c>
+      <c r="G188">
+        <v>257.92</v>
+      </c>
+      <c r="H188">
+        <v>4.29866666666666</v>
+      </c>
+    </row>
+    <row r="189" s="1" customFormat="1" ht="22.2" spans="1:5">
+      <c r="A189" s="16"/>
+      <c r="B189" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C189" s="12">
+        <v>46299</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="13">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="190" customFormat="1" spans="3:5">
+      <c r="C190" s="2"/>
+      <c r="D190"/>
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" customFormat="1" spans="1:8">
+      <c r="A191" t="s">
         <v>393</v>
       </c>
-      <c r="G188">
-        <v>285.04</v>
-      </c>
-      <c r="H188">
-        <v>4.75066666666666</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8">
-      <c r="A189" t="s">
+      <c r="B191" t="s">
         <v>394</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C191" s="2">
+        <v>46300</v>
+      </c>
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F191" t="s">
         <v>395</v>
       </c>
-      <c r="C189" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D189" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F189" t="s">
+      <c r="G191">
+        <v>193.75</v>
+      </c>
+      <c r="H191">
+        <v>3.22916666666666</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
         <v>396</v>
       </c>
-      <c r="G189">
-        <v>283.13</v>
-      </c>
-      <c r="H189">
-        <v>4.71883333333333</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8">
-      <c r="A190" t="s">
+      <c r="B192" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C192" s="2">
+        <v>46301</v>
+      </c>
+      <c r="D192" t="s">
+        <v>310</v>
+      </c>
+      <c r="E192" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="193" customFormat="1" spans="1:5">
+      <c r="A193" t="s">
+        <v>335</v>
+      </c>
+      <c r="B193" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="C190" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D190" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F190" t="s">
-        <v>399</v>
-      </c>
-      <c r="G190">
-        <v>236.71</v>
-      </c>
-      <c r="H190">
-        <v>3.94516666666666</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8">
-      <c r="A191" t="s">
-        <v>400</v>
-      </c>
-      <c r="B191" t="s">
-        <v>401</v>
-      </c>
-      <c r="C191" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D191" t="s">
-        <v>9</v>
-      </c>
-      <c r="E191" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F191" t="s">
-        <v>402</v>
-      </c>
-      <c r="G191">
-        <v>212.88</v>
-      </c>
-      <c r="H191">
-        <v>3.548</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8">
-      <c r="A192" t="s">
-        <v>403</v>
-      </c>
-      <c r="B192" t="s">
-        <v>404</v>
-      </c>
-      <c r="C192" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D192" t="s">
-        <v>9</v>
-      </c>
-      <c r="E192" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>405</v>
-      </c>
-      <c r="G192">
-        <v>232.96</v>
-      </c>
-      <c r="H192">
-        <v>3.88266666666666</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8">
-      <c r="A193" t="s">
-        <v>406</v>
-      </c>
-      <c r="B193" t="s">
-        <v>407</v>
-      </c>
       <c r="C193" s="2">
-        <v>46327</v>
+        <v>46302</v>
       </c>
       <c r="D193" t="s">
-        <v>9</v>
+        <v>310</v>
       </c>
       <c r="E193" s="3">
         <v>46327</v>
-      </c>
-      <c r="F193" t="s">
-        <v>408</v>
-      </c>
-      <c r="G193">
-        <v>251.54</v>
-      </c>
-      <c r="H193">
-        <v>4.19233333333333</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B194" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C194" s="2">
         <v>46327</v>
@@ -8468,21 +8394,21 @@
         <v>46327</v>
       </c>
       <c r="F194" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="G194">
-        <v>260.25</v>
+        <v>285.04</v>
       </c>
       <c r="H194">
-        <v>4.3375</v>
+        <v>4.75066666666666</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B195" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C195" s="2">
         <v>46327</v>
@@ -8494,21 +8420,21 @@
         <v>46327</v>
       </c>
       <c r="F195" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="G195">
-        <v>355.04</v>
+        <v>283.13</v>
       </c>
       <c r="H195">
-        <v>5.91733333333333</v>
+        <v>4.71883333333333</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B196" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C196" s="2">
         <v>46327</v>
@@ -8520,21 +8446,21 @@
         <v>46327</v>
       </c>
       <c r="F196" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="G196">
-        <v>271.21</v>
+        <v>236.71</v>
       </c>
       <c r="H196">
-        <v>4.52016666666666</v>
+        <v>3.94516666666666</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B197" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C197" s="2">
         <v>46327</v>
@@ -8546,21 +8472,21 @@
         <v>46327</v>
       </c>
       <c r="F197" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G197">
-        <v>230.25</v>
+        <v>212.88</v>
       </c>
       <c r="H197">
-        <v>3.8375</v>
+        <v>3.548</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B198" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C198" s="2">
         <v>46327</v>
@@ -8572,21 +8498,21 @@
         <v>46327</v>
       </c>
       <c r="F198" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="G198">
-        <v>272.42</v>
+        <v>232.96</v>
       </c>
       <c r="H198">
-        <v>4.54033333333333</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>3.88266666666666</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>91</v>
+        <v>414</v>
       </c>
       <c r="B199" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C199" s="2">
         <v>46327</v>
@@ -8596,14 +8522,23 @@
       </c>
       <c r="E199" s="3">
         <v>46327</v>
+      </c>
+      <c r="F199" t="s">
+        <v>416</v>
+      </c>
+      <c r="G199">
+        <v>251.54</v>
+      </c>
+      <c r="H199">
+        <v>4.19233333333333</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B200" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C200" s="2">
         <v>46327</v>
@@ -8615,38 +8550,47 @@
         <v>46327</v>
       </c>
       <c r="F200" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="G200">
-        <v>180.13</v>
+        <v>260.25</v>
       </c>
       <c r="H200">
-        <v>3.00216666666666</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>4.3375</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>427</v>
-      </c>
-      <c r="B201" s="8" t="s">
-        <v>428</v>
+        <v>420</v>
+      </c>
+      <c r="B201" t="s">
+        <v>421</v>
       </c>
       <c r="C201" s="2">
         <v>46327</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E201" s="3">
         <v>46327</v>
+      </c>
+      <c r="F201" t="s">
+        <v>422</v>
+      </c>
+      <c r="G201">
+        <v>355.04</v>
+      </c>
+      <c r="H201">
+        <v>5.91733333333333</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B202" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C202" s="2">
         <v>46327</v>
@@ -8658,21 +8602,21 @@
         <v>46327</v>
       </c>
       <c r="F202" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G202">
-        <v>246.71</v>
+        <v>271.21</v>
       </c>
       <c r="H202">
-        <v>4.11183333333333</v>
+        <v>4.52016666666666</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B203" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C203" s="2">
         <v>46327</v>
@@ -8684,21 +8628,21 @@
         <v>46327</v>
       </c>
       <c r="F203" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="G203">
-        <v>243.08</v>
+        <v>230.25</v>
       </c>
       <c r="H203">
-        <v>4.05133333333333</v>
+        <v>3.8375</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B204" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C204" s="2">
         <v>46327</v>
@@ -8710,21 +8654,21 @@
         <v>46327</v>
       </c>
       <c r="F204" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="G204">
-        <v>300.13</v>
+        <v>272.42</v>
       </c>
       <c r="H204">
-        <v>5.00216666666666</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8">
+        <v>4.54033333333333</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>432</v>
+        <v>91</v>
       </c>
       <c r="B205" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C205" s="2">
         <v>46327</v>
@@ -8735,74 +8679,30 @@
       <c r="E205" s="3">
         <v>46327</v>
       </c>
-      <c r="F205" t="s">
-        <v>438</v>
-      </c>
-      <c r="G205">
-        <v>258.21</v>
-      </c>
-      <c r="H205">
-        <v>4.3035</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8">
-      <c r="A206" t="s">
-        <v>432</v>
-      </c>
-      <c r="B206" t="s">
-        <v>439</v>
-      </c>
-      <c r="C206" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D206" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F206" t="s">
-        <v>440</v>
-      </c>
-      <c r="G206">
-        <v>211.329999999999</v>
-      </c>
-      <c r="H206">
-        <v>3.52216666666666</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
+    </row>
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
         <v>432</v>
       </c>
-      <c r="B207" t="s">
-        <v>441</v>
+      <c r="B207" s="8" t="s">
+        <v>433</v>
       </c>
       <c r="C207" s="2">
         <v>46327</v>
       </c>
       <c r="D207" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E207" s="3">
         <v>46327</v>
-      </c>
-      <c r="F207" t="s">
-        <v>442</v>
-      </c>
-      <c r="G207">
-        <v>191.88</v>
-      </c>
-      <c r="H207">
-        <v>3.198</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B208" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C208" s="2">
         <v>46327</v>
@@ -8814,21 +8714,21 @@
         <v>46327</v>
       </c>
       <c r="F208" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="G208">
-        <v>431.42</v>
+        <v>246.71</v>
       </c>
       <c r="H208">
-        <v>7.19033333333333</v>
+        <v>4.11183333333333</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B209" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C209" s="2">
         <v>46327</v>
@@ -8840,21 +8740,21 @@
         <v>46327</v>
       </c>
       <c r="F209" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="G209">
-        <v>147.25</v>
+        <v>243.08</v>
       </c>
       <c r="H209">
-        <v>2.45416666666666</v>
+        <v>4.05133333333333</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B210" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C210" s="2">
         <v>46327</v>
@@ -8866,21 +8766,21 @@
         <v>46327</v>
       </c>
       <c r="F210" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="G210">
-        <v>186.88</v>
+        <v>300.13</v>
       </c>
       <c r="H210">
-        <v>3.11466666666666</v>
+        <v>5.00216666666666</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B211" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C211" s="2">
         <v>46327</v>
@@ -8892,21 +8792,21 @@
         <v>46327</v>
       </c>
       <c r="F211" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="G211">
-        <v>188</v>
+        <v>258.21</v>
       </c>
       <c r="H211">
-        <v>3.13333333333333</v>
+        <v>4.3035</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B212" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C212" s="2">
         <v>46327</v>
@@ -8918,21 +8818,21 @@
         <v>46327</v>
       </c>
       <c r="F212" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="G212">
-        <v>250.63</v>
+        <v>211.329999999999</v>
       </c>
       <c r="H212">
-        <v>4.17716666666666</v>
+        <v>3.52216666666666</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B213" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C213" s="2">
         <v>46327</v>
@@ -8944,21 +8844,21 @@
         <v>46327</v>
       </c>
       <c r="F213" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G213">
-        <v>285.04</v>
+        <v>191.88</v>
       </c>
       <c r="H213">
-        <v>4.75066666666666</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B214" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C214" s="2">
         <v>46327</v>
@@ -8970,21 +8870,21 @@
         <v>46327</v>
       </c>
       <c r="F214" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G214">
-        <v>127.5</v>
+        <v>431.42</v>
       </c>
       <c r="H214">
-        <v>2.125</v>
+        <v>7.19033333333333</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="B215" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C215" s="2">
         <v>46327</v>
@@ -8996,21 +8896,21 @@
         <v>46327</v>
       </c>
       <c r="F215" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="G215">
-        <v>237.88</v>
+        <v>147.25</v>
       </c>
       <c r="H215">
-        <v>3.96466666666666</v>
+        <v>2.45416666666666</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="B216" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C216" s="2">
         <v>46327</v>
@@ -9022,21 +8922,21 @@
         <v>46327</v>
       </c>
       <c r="F216" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="G216">
-        <v>260.79</v>
+        <v>186.88</v>
       </c>
       <c r="H216">
-        <v>4.3465</v>
+        <v>3.11466666666666</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="B217" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C217" s="2">
         <v>46327</v>
@@ -9048,47 +8948,47 @@
         <v>46327</v>
       </c>
       <c r="F217" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="G217">
-        <v>189.79</v>
+        <v>188</v>
       </c>
       <c r="H217">
-        <v>3.16316666666666</v>
+        <v>3.13333333333333</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
+        <v>437</v>
+      </c>
+      <c r="B218" t="s">
+        <v>456</v>
+      </c>
+      <c r="C218" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D218" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F218" t="s">
         <v>457</v>
       </c>
-      <c r="B218" t="s">
-        <v>464</v>
-      </c>
-      <c r="C218" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D218" t="s">
-        <v>9</v>
-      </c>
-      <c r="E218" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F218" t="s">
-        <v>465</v>
-      </c>
       <c r="G218">
-        <v>170.79</v>
+        <v>250.63</v>
       </c>
       <c r="H218">
-        <v>2.8465</v>
+        <v>4.17716666666666</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="B219" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C219" s="2">
         <v>46327</v>
@@ -9100,21 +9000,21 @@
         <v>46327</v>
       </c>
       <c r="F219" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G219">
-        <v>174.13</v>
+        <v>285.04</v>
       </c>
       <c r="H219">
-        <v>2.90216666666666</v>
+        <v>4.75066666666666</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="B220" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C220" s="2">
         <v>46327</v>
@@ -9126,21 +9026,21 @@
         <v>46327</v>
       </c>
       <c r="F220" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="G220">
-        <v>208.829999999999</v>
+        <v>127.5</v>
       </c>
       <c r="H220">
-        <v>3.48049999999999</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B221" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C221" s="2">
         <v>46327</v>
@@ -9152,21 +9052,21 @@
         <v>46327</v>
       </c>
       <c r="F221" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G221">
-        <v>287.75</v>
+        <v>237.88</v>
       </c>
       <c r="H221">
-        <v>4.79583333333333</v>
+        <v>3.96466666666666</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B222" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C222" s="2">
         <v>46327</v>
@@ -9178,21 +9078,21 @@
         <v>46327</v>
       </c>
       <c r="F222" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G222">
-        <v>182.21</v>
+        <v>260.79</v>
       </c>
       <c r="H222">
-        <v>3.03683333333333</v>
+        <v>4.3465</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B223" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C223" s="2">
         <v>46327</v>
@@ -9204,21 +9104,21 @@
         <v>46327</v>
       </c>
       <c r="F223" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G223">
-        <v>299.25</v>
+        <v>189.79</v>
       </c>
       <c r="H223">
-        <v>4.9875</v>
+        <v>3.16316666666666</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B224" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C224" s="2">
         <v>46327</v>
@@ -9230,21 +9130,21 @@
         <v>46327</v>
       </c>
       <c r="F224" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="G224">
-        <v>303.5</v>
+        <v>170.79</v>
       </c>
       <c r="H224">
-        <v>5.05833333333333</v>
+        <v>2.8465</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B225" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="C225" s="2">
         <v>46327</v>
@@ -9256,21 +9156,21 @@
         <v>46327</v>
       </c>
       <c r="F225" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G225">
-        <v>205.079999999999</v>
+        <v>174.13</v>
       </c>
       <c r="H225">
-        <v>3.41799999999999</v>
+        <v>2.90216666666666</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B226" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C226" s="2">
         <v>46327</v>
@@ -9282,21 +9182,21 @@
         <v>46327</v>
       </c>
       <c r="F226" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="G226">
-        <v>262.33</v>
+        <v>208.829999999999</v>
       </c>
       <c r="H226">
-        <v>4.37216666666666</v>
+        <v>3.48049999999999</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C227" s="2">
         <v>46327</v>
@@ -9308,21 +9208,21 @@
         <v>46327</v>
       </c>
       <c r="F227" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G227">
-        <v>206.04</v>
+        <v>287.75</v>
       </c>
       <c r="H227">
-        <v>3.43399999999999</v>
+        <v>4.79583333333333</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="B228" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C228" s="2">
         <v>46327</v>
@@ -9334,21 +9234,21 @@
         <v>46327</v>
       </c>
       <c r="F228" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="G228">
-        <v>211.13</v>
+        <v>182.21</v>
       </c>
       <c r="H228">
-        <v>3.51883333333333</v>
+        <v>3.03683333333333</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="B229" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C229" s="2">
         <v>46327</v>
@@ -9360,21 +9260,21 @@
         <v>46327</v>
       </c>
       <c r="F229" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G229">
-        <v>200.54</v>
+        <v>299.25</v>
       </c>
       <c r="H229">
-        <v>3.34233333333333</v>
+        <v>4.9875</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>11</v>
+        <v>462</v>
       </c>
       <c r="B230" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C230" s="2">
         <v>46327</v>
@@ -9386,21 +9286,21 @@
         <v>46327</v>
       </c>
       <c r="F230" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G230">
-        <v>170.17</v>
+        <v>303.5</v>
       </c>
       <c r="H230">
-        <v>2.83616666666666</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
+        <v>5.05833333333333</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>491</v>
-      </c>
-      <c r="B231" s="8" t="s">
-        <v>492</v>
+        <v>462</v>
+      </c>
+      <c r="B231" t="s">
+        <v>483</v>
       </c>
       <c r="C231" s="2">
         <v>46327</v>
@@ -9410,14 +9310,23 @@
       </c>
       <c r="E231" s="3">
         <v>46327</v>
+      </c>
+      <c r="F231" t="s">
+        <v>484</v>
+      </c>
+      <c r="G231">
+        <v>205.079999999999</v>
+      </c>
+      <c r="H231">
+        <v>3.41799999999999</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>493</v>
+        <v>462</v>
       </c>
       <c r="B232" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C232" s="2">
         <v>46327</v>
@@ -9429,21 +9338,21 @@
         <v>46327</v>
       </c>
       <c r="F232" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="G232">
-        <v>169.13</v>
+        <v>262.33</v>
       </c>
       <c r="H232">
-        <v>2.81883333333333</v>
+        <v>4.37216666666666</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B233" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C233" s="2">
         <v>46327</v>
@@ -9455,21 +9364,21 @@
         <v>46327</v>
       </c>
       <c r="F233" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G233">
-        <v>151.54</v>
+        <v>206.04</v>
       </c>
       <c r="H233">
-        <v>2.52566666666666</v>
+        <v>3.43399999999999</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B234" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C234" s="2">
         <v>46327</v>
@@ -9481,47 +9390,47 @@
         <v>46327</v>
       </c>
       <c r="F234" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G234">
-        <v>369.83</v>
+        <v>211.13</v>
       </c>
       <c r="H234">
-        <v>6.16383333333333</v>
+        <v>3.51883333333333</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
+        <v>487</v>
+      </c>
+      <c r="B235" t="s">
+        <v>492</v>
+      </c>
+      <c r="C235" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D235" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F235" t="s">
         <v>493</v>
       </c>
-      <c r="B235" t="s">
-        <v>500</v>
-      </c>
-      <c r="C235" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D235" t="s">
-        <v>9</v>
-      </c>
-      <c r="E235" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F235" t="s">
-        <v>501</v>
-      </c>
       <c r="G235">
-        <v>332.13</v>
+        <v>200.54</v>
       </c>
       <c r="H235">
-        <v>5.5355</v>
+        <v>3.34233333333333</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
-        <v>493</v>
+        <v>11</v>
       </c>
       <c r="B236" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C236" s="2">
         <v>46327</v>
@@ -9533,21 +9442,21 @@
         <v>46327</v>
       </c>
       <c r="F236" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="G236">
-        <v>267.92</v>
+        <v>170.17</v>
       </c>
       <c r="H236">
-        <v>4.46533333333333</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8">
+        <v>2.83616666666666</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>493</v>
-      </c>
-      <c r="B237" t="s">
-        <v>504</v>
+        <v>496</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>497</v>
       </c>
       <c r="C237" s="2">
         <v>46327</v>
@@ -9557,23 +9466,14 @@
       </c>
       <c r="E237" s="3">
         <v>46327</v>
-      </c>
-      <c r="F237" t="s">
-        <v>505</v>
-      </c>
-      <c r="G237">
-        <v>196.63</v>
-      </c>
-      <c r="H237">
-        <v>3.27716666666666</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B238" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C238" s="2">
         <v>46327</v>
@@ -9585,21 +9485,21 @@
         <v>46327</v>
       </c>
       <c r="F238" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="G238">
-        <v>413.38</v>
+        <v>169.13</v>
       </c>
       <c r="H238">
-        <v>6.88966666666666</v>
+        <v>2.81883333333333</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="B239" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C239" s="2">
         <v>46327</v>
@@ -9611,21 +9511,21 @@
         <v>46327</v>
       </c>
       <c r="F239" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="G239">
-        <v>333.96</v>
+        <v>151.54</v>
       </c>
       <c r="H239">
-        <v>5.566</v>
+        <v>2.52566666666666</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B240" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C240" s="2">
         <v>46327</v>
@@ -9637,21 +9537,21 @@
         <v>46327</v>
       </c>
       <c r="F240" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="G240">
-        <v>254.13</v>
+        <v>369.83</v>
       </c>
       <c r="H240">
-        <v>4.2355</v>
+        <v>6.16383333333333</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B241" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="C241" s="2">
         <v>46327</v>
@@ -9663,21 +9563,21 @@
         <v>46327</v>
       </c>
       <c r="F241" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="G241">
-        <v>233.38</v>
+        <v>332.13</v>
       </c>
       <c r="H241">
-        <v>3.88966666666666</v>
+        <v>5.5355</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="B242" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C242" s="2">
         <v>46327</v>
@@ -9689,21 +9589,21 @@
         <v>46327</v>
       </c>
       <c r="F242" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="G242">
-        <v>231.79</v>
+        <v>267.92</v>
       </c>
       <c r="H242">
-        <v>3.86316666666666</v>
+        <v>4.46533333333333</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="B243" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C243" s="2">
         <v>46327</v>
@@ -9715,21 +9615,21 @@
         <v>46327</v>
       </c>
       <c r="F243" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="G243">
-        <v>248.88</v>
+        <v>196.63</v>
       </c>
       <c r="H243">
-        <v>4.148</v>
+        <v>3.27716666666666</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="B244" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="C244" s="2">
         <v>46327</v>
@@ -9741,21 +9641,21 @@
         <v>46327</v>
       </c>
       <c r="F244" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="G244">
-        <v>284.96</v>
+        <v>413.38</v>
       </c>
       <c r="H244">
-        <v>4.74933333333333</v>
+        <v>6.88966666666666</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="B245" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="C245" s="2">
         <v>46327</v>
@@ -9767,21 +9667,21 @@
         <v>46327</v>
       </c>
       <c r="F245" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="G245">
-        <v>254.71</v>
+        <v>333.96</v>
       </c>
       <c r="H245">
-        <v>4.24516666666666</v>
+        <v>5.566</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="B246" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C246" s="2">
         <v>46327</v>
@@ -9793,21 +9693,21 @@
         <v>46327</v>
       </c>
       <c r="F246" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="G246">
-        <v>216.71</v>
+        <v>254.13</v>
       </c>
       <c r="H246">
-        <v>3.61183333333333</v>
+        <v>4.2355</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B247" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C247" s="2">
         <v>46327</v>
@@ -9819,21 +9719,21 @@
         <v>46327</v>
       </c>
       <c r="F247" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="G247">
-        <v>151</v>
+        <v>233.38</v>
       </c>
       <c r="H247">
-        <v>2.51666666666666</v>
+        <v>3.88966666666666</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B248" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="C248" s="2">
         <v>46327</v>
@@ -9845,21 +9745,21 @@
         <v>46327</v>
       </c>
       <c r="F248" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="G248">
-        <v>188.42</v>
+        <v>231.79</v>
       </c>
       <c r="H248">
-        <v>3.14033333333333</v>
+        <v>3.86316666666666</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B249" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C249" s="2">
         <v>46327</v>
@@ -9871,22 +9771,22 @@
         <v>46327</v>
       </c>
       <c r="F249" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="G249">
-        <v>188.08</v>
+        <v>248.88</v>
       </c>
       <c r="H249">
-        <v>3.13466666666666</v>
+        <v>4.148</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
+        <v>529</v>
+      </c>
+      <c r="B250" t="s">
         <v>530</v>
       </c>
-      <c r="B250" t="s">
-        <v>539</v>
-      </c>
       <c r="C250" s="2">
         <v>46327</v>
       </c>
@@ -9897,98 +9797,125 @@
         <v>46327</v>
       </c>
       <c r="F250" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G250">
-        <v>153.38</v>
+        <v>284.96</v>
       </c>
       <c r="H250">
-        <v>2.55633333333333</v>
+        <v>4.74933333333333</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B251" t="s">
+        <v>533</v>
+      </c>
+      <c r="C251" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F251" t="s">
+        <v>534</v>
+      </c>
+      <c r="G251">
+        <v>254.71</v>
+      </c>
+      <c r="H251">
+        <v>4.24516666666666</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" t="s">
+        <v>535</v>
+      </c>
+      <c r="B252" t="s">
+        <v>536</v>
+      </c>
+      <c r="C252" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F252" t="s">
+        <v>537</v>
+      </c>
+      <c r="G252">
+        <v>216.71</v>
+      </c>
+      <c r="H252">
+        <v>3.61183333333333</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" t="s">
+        <v>535</v>
+      </c>
+      <c r="B253" t="s">
+        <v>538</v>
+      </c>
+      <c r="C253" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D253" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F253" t="s">
+        <v>539</v>
+      </c>
+      <c r="G253">
+        <v>151</v>
+      </c>
+      <c r="H253">
+        <v>2.51666666666666</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" t="s">
+        <v>535</v>
+      </c>
+      <c r="B254" t="s">
+        <v>540</v>
+      </c>
+      <c r="C254" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F254" t="s">
         <v>541</v>
       </c>
-      <c r="C251" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D251" t="s">
-        <v>9</v>
-      </c>
-      <c r="E251" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F251" t="s">
-        <v>542</v>
-      </c>
-      <c r="G251">
-        <v>198.5</v>
-      </c>
-      <c r="H251">
-        <v>3.30833333333333</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
-      <c r="A252" t="s">
-        <v>94</v>
-      </c>
-      <c r="B252" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="C252" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D252" t="s">
-        <v>9</v>
-      </c>
-      <c r="E252" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
-      <c r="A253" t="s">
-        <v>94</v>
-      </c>
-      <c r="B253" t="s">
-        <v>544</v>
-      </c>
-      <c r="C253" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D253" t="s">
-        <v>16</v>
-      </c>
-      <c r="E253" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
-      <c r="A254" t="s">
-        <v>94</v>
-      </c>
-      <c r="B254" t="s">
-        <v>545</v>
-      </c>
-      <c r="C254" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D254" t="s">
-        <v>16</v>
-      </c>
-      <c r="E254" s="3">
-        <v>46327</v>
+      <c r="G254">
+        <v>188.42</v>
+      </c>
+      <c r="H254">
+        <v>3.14033333333333</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="B255" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C255" s="2">
         <v>46327</v>
@@ -10000,21 +9927,21 @@
         <v>46327</v>
       </c>
       <c r="F255" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="G255">
-        <v>220.75</v>
+        <v>188.08</v>
       </c>
       <c r="H255">
-        <v>3.67916666666666</v>
+        <v>3.13466666666666</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="B256" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C256" s="2">
         <v>46327</v>
@@ -10026,22 +9953,22 @@
         <v>46327</v>
       </c>
       <c r="F256" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G256">
-        <v>236.829999999999</v>
+        <v>153.38</v>
       </c>
       <c r="H256">
-        <v>3.94716666666666</v>
+        <v>2.55633333333333</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
+        <v>535</v>
+      </c>
+      <c r="B257" t="s">
         <v>546</v>
       </c>
-      <c r="B257" t="s">
-        <v>551</v>
-      </c>
       <c r="C257" s="2">
         <v>46327</v>
       </c>
@@ -10052,21 +9979,21 @@
         <v>46327</v>
       </c>
       <c r="F257" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="G257">
-        <v>214.21</v>
+        <v>198.5</v>
       </c>
       <c r="H257">
-        <v>3.57016666666666</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
+        <v>3.30833333333333</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>553</v>
-      </c>
-      <c r="B258" t="s">
-        <v>554</v>
+        <v>94</v>
+      </c>
+      <c r="B258" s="14" t="s">
+        <v>548</v>
       </c>
       <c r="C258" s="2">
         <v>46327</v>
@@ -10077,100 +10004,73 @@
       <c r="E258" s="3">
         <v>46327</v>
       </c>
-      <c r="F258" t="s">
-        <v>555</v>
-      </c>
-      <c r="G258">
-        <v>454.25</v>
-      </c>
-      <c r="H258">
-        <v>7.57083333333333</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8">
+    </row>
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>553</v>
+        <v>94</v>
       </c>
       <c r="B259" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C259" s="2">
         <v>46327</v>
       </c>
       <c r="D259" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E259" s="3">
         <v>46327</v>
       </c>
-      <c r="F259" t="s">
-        <v>557</v>
-      </c>
-      <c r="G259">
-        <v>330.5</v>
-      </c>
-      <c r="H259">
-        <v>5.50833333333333</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8">
+    </row>
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>553</v>
+        <v>94</v>
       </c>
       <c r="B260" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C260" s="2">
         <v>46327</v>
       </c>
       <c r="D260" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E260" s="3">
         <v>46327</v>
-      </c>
-      <c r="F260" t="s">
-        <v>559</v>
-      </c>
-      <c r="G260">
-        <v>208.88</v>
-      </c>
-      <c r="H260">
-        <v>3.48133333333333</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B261" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="C261" s="2">
         <v>46327</v>
       </c>
       <c r="D261" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E261" s="3">
         <v>46327</v>
       </c>
       <c r="F261" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="G261">
-        <v>296.13</v>
+        <v>220.75</v>
       </c>
       <c r="H261">
-        <v>4.9355</v>
+        <v>3.67916666666666</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B262" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="C262" s="2">
         <v>46327</v>
@@ -10182,21 +10082,21 @@
         <v>46327</v>
       </c>
       <c r="F262" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="G262">
-        <v>234.079999999999</v>
+        <v>236.829999999999</v>
       </c>
       <c r="H262">
-        <v>3.90133333333333</v>
+        <v>3.94716666666666</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B263" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="C263" s="2">
         <v>46327</v>
@@ -10208,21 +10108,21 @@
         <v>46327</v>
       </c>
       <c r="F263" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="G263">
-        <v>235.54</v>
+        <v>214.21</v>
       </c>
       <c r="H263">
-        <v>3.92566666666666</v>
+        <v>3.57016666666666</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B264" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="C264" s="2">
         <v>46327</v>
@@ -10234,21 +10134,21 @@
         <v>46327</v>
       </c>
       <c r="F264" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G264">
-        <v>186.46</v>
+        <v>454.25</v>
       </c>
       <c r="H264">
-        <v>3.10766666666666</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
+        <v>7.57083333333333</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>570</v>
-      </c>
-      <c r="B265" s="8" t="s">
-        <v>571</v>
+        <v>558</v>
+      </c>
+      <c r="B265" t="s">
+        <v>561</v>
       </c>
       <c r="C265" s="2">
         <v>46327</v>
@@ -10258,14 +10158,23 @@
       </c>
       <c r="E265" s="3">
         <v>46327</v>
+      </c>
+      <c r="F265" t="s">
+        <v>562</v>
+      </c>
+      <c r="G265">
+        <v>330.5</v>
+      </c>
+      <c r="H265">
+        <v>5.50833333333333</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="B266" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="C266" s="2">
         <v>46327</v>
@@ -10277,47 +10186,47 @@
         <v>46327</v>
       </c>
       <c r="F266" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="G266">
-        <v>237.96</v>
+        <v>208.88</v>
       </c>
       <c r="H266">
-        <v>3.966</v>
+        <v>3.48133333333333</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B267" t="s">
-        <v>413</v>
+        <v>566</v>
       </c>
       <c r="C267" s="2">
         <v>46327</v>
       </c>
       <c r="D267" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E267" s="3">
         <v>46327</v>
       </c>
       <c r="F267" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="G267">
-        <v>277.08</v>
+        <v>296.13</v>
       </c>
       <c r="H267">
-        <v>4.61799999999999</v>
+        <v>4.9355</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B268" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C268" s="2">
         <v>46327</v>
@@ -10329,21 +10238,21 @@
         <v>46327</v>
       </c>
       <c r="F268" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="G268">
-        <v>209.88</v>
+        <v>234.079999999999</v>
       </c>
       <c r="H268">
-        <v>3.49799999999999</v>
+        <v>3.90133333333333</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B269" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C269" s="2">
         <v>46327</v>
@@ -10355,13 +10264,13 @@
         <v>46327</v>
       </c>
       <c r="F269" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="G269">
-        <v>280.54</v>
+        <v>235.54</v>
       </c>
       <c r="H269">
-        <v>4.67566666666666</v>
+        <v>3.92566666666666</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -10369,7 +10278,7 @@
         <v>572</v>
       </c>
       <c r="B270" t="s">
-        <v>359</v>
+        <v>573</v>
       </c>
       <c r="C270" s="2">
         <v>46327</v>
@@ -10381,21 +10290,21 @@
         <v>46327</v>
       </c>
       <c r="F270" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="G270">
-        <v>287.67</v>
+        <v>186.46</v>
       </c>
       <c r="H270">
-        <v>4.7945</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8">
+        <v>3.10766666666666</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>572</v>
-      </c>
-      <c r="B271" t="s">
-        <v>581</v>
+        <v>575</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>576</v>
       </c>
       <c r="C271" s="2">
         <v>46327</v>
@@ -10405,23 +10314,14 @@
       </c>
       <c r="E271" s="3">
         <v>46327</v>
-      </c>
-      <c r="F271" t="s">
-        <v>582</v>
-      </c>
-      <c r="G271">
-        <v>274.71</v>
-      </c>
-      <c r="H271">
-        <v>4.5785</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B272" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C272" s="2">
         <v>46327</v>
@@ -10433,21 +10333,21 @@
         <v>46327</v>
       </c>
       <c r="F272" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="G272">
-        <v>161.13</v>
+        <v>237.96</v>
       </c>
       <c r="H272">
-        <v>2.68549999999999</v>
+        <v>3.966</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B273" t="s">
-        <v>586</v>
+        <v>421</v>
       </c>
       <c r="C273" s="2">
         <v>46327</v>
@@ -10459,21 +10359,21 @@
         <v>46327</v>
       </c>
       <c r="F273" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="G273">
-        <v>176.96</v>
+        <v>277.08</v>
       </c>
       <c r="H273">
-        <v>2.94933333333333</v>
+        <v>4.61799999999999</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B274" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C274" s="2">
         <v>46327</v>
@@ -10485,21 +10385,21 @@
         <v>46327</v>
       </c>
       <c r="F274" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="G274">
-        <v>193.75</v>
+        <v>209.88</v>
       </c>
       <c r="H274">
-        <v>3.22916666666666</v>
+        <v>3.49799999999999</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>282</v>
+        <v>577</v>
       </c>
       <c r="B275" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C275" s="2">
         <v>46327</v>
@@ -10511,21 +10411,21 @@
         <v>46327</v>
       </c>
       <c r="F275" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G275">
-        <v>255.96</v>
+        <v>280.54</v>
       </c>
       <c r="H275">
-        <v>4.266</v>
+        <v>4.67566666666666</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>282</v>
+        <v>577</v>
       </c>
       <c r="B276" t="s">
-        <v>592</v>
+        <v>359</v>
       </c>
       <c r="C276" s="2">
         <v>46327</v>
@@ -10537,21 +10437,21 @@
         <v>46327</v>
       </c>
       <c r="F276" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G276">
-        <v>242.25</v>
+        <v>287.67</v>
       </c>
       <c r="H276">
-        <v>4.0375</v>
+        <v>4.7945</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>330</v>
+        <v>577</v>
       </c>
       <c r="B277" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C277" s="2">
         <v>46327</v>
@@ -10563,21 +10463,21 @@
         <v>46327</v>
       </c>
       <c r="F277" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="G277">
-        <v>253.33</v>
+        <v>274.71</v>
       </c>
       <c r="H277">
-        <v>4.22216666666666</v>
+        <v>4.5785</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="B278" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C278" s="2">
         <v>46327</v>
@@ -10589,21 +10489,21 @@
         <v>46327</v>
       </c>
       <c r="F278" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="G278">
-        <v>277.46</v>
+        <v>161.13</v>
       </c>
       <c r="H278">
-        <v>4.62433333333333</v>
+        <v>2.68549999999999</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
-        <v>598</v>
+        <v>393</v>
       </c>
       <c r="B279" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="C279" s="2">
         <v>46327</v>
@@ -10615,21 +10515,21 @@
         <v>46327</v>
       </c>
       <c r="F279" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="G279">
-        <v>135.17</v>
+        <v>176.96</v>
       </c>
       <c r="H279">
-        <v>2.25283333333333</v>
+        <v>2.94933333333333</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>598</v>
+        <v>393</v>
       </c>
       <c r="B280" t="s">
-        <v>601</v>
+        <v>394</v>
       </c>
       <c r="C280" s="2">
         <v>46327</v>
@@ -10641,21 +10541,21 @@
         <v>46327</v>
       </c>
       <c r="F280" t="s">
-        <v>602</v>
+        <v>395</v>
       </c>
       <c r="G280">
-        <v>178.38</v>
+        <v>193.75</v>
       </c>
       <c r="H280">
-        <v>2.973</v>
+        <v>3.22916666666666</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>598</v>
+        <v>282</v>
       </c>
       <c r="B281" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="C281" s="2">
         <v>46327</v>
@@ -10667,21 +10567,21 @@
         <v>46327</v>
       </c>
       <c r="F281" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="G281">
-        <v>137.13</v>
+        <v>255.96</v>
       </c>
       <c r="H281">
-        <v>2.2855</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
-        <v>598</v>
+        <v>282</v>
       </c>
       <c r="B282" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="C282" s="2">
         <v>46327</v>
@@ -10693,21 +10593,21 @@
         <v>46327</v>
       </c>
       <c r="F282" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="G282">
-        <v>160.25</v>
+        <v>242.25</v>
       </c>
       <c r="H282">
-        <v>2.67083333333333</v>
+        <v>4.0375</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>598</v>
+        <v>330</v>
       </c>
       <c r="B283" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C283" s="2">
         <v>46327</v>
@@ -10719,22 +10619,22 @@
         <v>46327</v>
       </c>
       <c r="F283" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="G283">
-        <v>184.46</v>
+        <v>253.33</v>
       </c>
       <c r="H283">
-        <v>3.07433333333333</v>
+        <v>4.22216666666666</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
+        <v>330</v>
+      </c>
+      <c r="B284" t="s">
         <v>598</v>
       </c>
-      <c r="B284" t="s">
-        <v>609</v>
-      </c>
       <c r="C284" s="2">
         <v>46327</v>
       </c>
@@ -10745,21 +10645,21 @@
         <v>46327</v>
       </c>
       <c r="F284" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="G284">
-        <v>144.04</v>
+        <v>277.46</v>
       </c>
       <c r="H284">
-        <v>2.40066666666666</v>
+        <v>4.62433333333333</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="B285" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="C285" s="2">
         <v>46327</v>
@@ -10771,21 +10671,21 @@
         <v>46327</v>
       </c>
       <c r="F285" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="G285">
-        <v>185.88</v>
+        <v>135.17</v>
       </c>
       <c r="H285">
-        <v>3.098</v>
+        <v>2.25283333333333</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="B286" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="C286" s="2">
         <v>46327</v>
@@ -10797,21 +10697,21 @@
         <v>46327</v>
       </c>
       <c r="F286" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="G286">
-        <v>174.17</v>
+        <v>178.38</v>
       </c>
       <c r="H286">
-        <v>2.90283333333333</v>
+        <v>2.973</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="B287" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="C287" s="2">
         <v>46327</v>
@@ -10823,21 +10723,21 @@
         <v>46327</v>
       </c>
       <c r="F287" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="G287">
-        <v>232.5</v>
+        <v>137.13</v>
       </c>
       <c r="H287">
-        <v>3.875</v>
+        <v>2.2855</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="B288" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="C288" s="2">
         <v>46327</v>
@@ -10849,21 +10749,21 @@
         <v>46327</v>
       </c>
       <c r="F288" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="G288">
-        <v>269.54</v>
+        <v>160.25</v>
       </c>
       <c r="H288">
-        <v>4.49233333333333</v>
+        <v>2.67083333333333</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="B289" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C289" s="2">
         <v>46327</v>
@@ -10875,21 +10775,21 @@
         <v>46327</v>
       </c>
       <c r="F289" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="G289">
-        <v>238.5</v>
+        <v>184.46</v>
       </c>
       <c r="H289">
-        <v>3.975</v>
+        <v>3.07433333333333</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="B290" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C290" s="2">
         <v>46327</v>
@@ -10901,21 +10801,21 @@
         <v>46327</v>
       </c>
       <c r="F290" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="G290">
-        <v>219.25</v>
+        <v>144.04</v>
       </c>
       <c r="H290">
-        <v>3.65416666666666</v>
+        <v>2.40066666666666</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B291" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C291" s="2">
         <v>46327</v>
@@ -10927,21 +10827,21 @@
         <v>46327</v>
       </c>
       <c r="F291" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="G291">
-        <v>266.83</v>
+        <v>185.88</v>
       </c>
       <c r="H291">
-        <v>4.44716666666666</v>
+        <v>3.098</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B292" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C292" s="2">
         <v>46327</v>
@@ -10953,21 +10853,21 @@
         <v>46327</v>
       </c>
       <c r="F292" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="G292">
-        <v>297.08</v>
+        <v>174.17</v>
       </c>
       <c r="H292">
-        <v>4.95133333333333</v>
+        <v>2.90283333333333</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B293" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C293" s="2">
         <v>46327</v>
@@ -10979,21 +10879,21 @@
         <v>46327</v>
       </c>
       <c r="F293" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="G293">
-        <v>246.5</v>
+        <v>232.5</v>
       </c>
       <c r="H293">
-        <v>4.10833333333333</v>
+        <v>3.875</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B294" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C294" s="2">
         <v>46327</v>
@@ -11005,21 +10905,21 @@
         <v>46327</v>
       </c>
       <c r="F294" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="G294">
-        <v>266</v>
+        <v>269.54</v>
       </c>
       <c r="H294">
-        <v>4.43333333333333</v>
+        <v>4.49233333333333</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B295" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C295" s="2">
         <v>46327</v>
@@ -11031,21 +10931,21 @@
         <v>46327</v>
       </c>
       <c r="F295" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="G295">
-        <v>309.29</v>
+        <v>238.5</v>
       </c>
       <c r="H295">
-        <v>5.15483333333333</v>
+        <v>3.975</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B296" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="C296" s="2">
         <v>46327</v>
@@ -11057,21 +10957,21 @@
         <v>46327</v>
       </c>
       <c r="F296" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="G296">
-        <v>251.04</v>
+        <v>219.25</v>
       </c>
       <c r="H296">
-        <v>4.184</v>
+        <v>3.65416666666666</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="B297" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C297" s="2">
         <v>46327</v>
@@ -11083,21 +10983,21 @@
         <v>46327</v>
       </c>
       <c r="F297" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="G297">
-        <v>236.04</v>
+        <v>266.83</v>
       </c>
       <c r="H297">
-        <v>3.93399999999999</v>
+        <v>4.44716666666666</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="B298" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="C298" s="2">
         <v>46327</v>
@@ -11109,21 +11009,21 @@
         <v>46327</v>
       </c>
       <c r="F298" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="G298">
-        <v>615.54</v>
+        <v>297.08</v>
       </c>
       <c r="H298">
-        <v>10.2589999999999</v>
+        <v>4.95133333333333</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="B299" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C299" s="2">
         <v>46327</v>
@@ -11135,21 +11035,21 @@
         <v>46327</v>
       </c>
       <c r="F299" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="G299">
-        <v>367.42</v>
+        <v>246.5</v>
       </c>
       <c r="H299">
-        <v>6.12366666666666</v>
+        <v>4.10833333333333</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B300" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C300" s="2">
         <v>46327</v>
@@ -11161,21 +11061,21 @@
         <v>46327</v>
       </c>
       <c r="F300" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="G300">
-        <v>342.08</v>
+        <v>266</v>
       </c>
       <c r="H300">
-        <v>5.70133333333333</v>
+        <v>4.43333333333333</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="B301" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C301" s="2">
         <v>46327</v>
@@ -11187,21 +11087,21 @@
         <v>46327</v>
       </c>
       <c r="F301" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="G301">
-        <v>221.21</v>
+        <v>309.29</v>
       </c>
       <c r="H301">
-        <v>3.68683333333333</v>
+        <v>5.15483333333333</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="B302" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="C302" s="2">
         <v>46327</v>
@@ -11213,21 +11113,21 @@
         <v>46327</v>
       </c>
       <c r="F302" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="G302">
-        <v>193.71</v>
+        <v>251.04</v>
       </c>
       <c r="H302">
-        <v>3.2285</v>
+        <v>4.184</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="B303" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="C303" s="2">
         <v>46327</v>
@@ -11239,81 +11139,99 @@
         <v>46327</v>
       </c>
       <c r="F303" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="G303">
-        <v>221.25</v>
+        <v>236.04</v>
       </c>
       <c r="H303">
-        <v>3.6875</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5">
+        <v>3.93399999999999</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="B304" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C304" s="2">
         <v>46327</v>
       </c>
       <c r="D304" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E304" s="3">
         <v>46327</v>
       </c>
-    </row>
-    <row r="305" spans="1:5">
+      <c r="F304" t="s">
+        <v>646</v>
+      </c>
+      <c r="G304">
+        <v>615.54</v>
+      </c>
+      <c r="H304">
+        <v>10.2589999999999</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
       <c r="A305" t="s">
-        <v>658</v>
-      </c>
-      <c r="B305" s="8" t="s">
-        <v>659</v>
+        <v>644</v>
+      </c>
+      <c r="B305" t="s">
+        <v>647</v>
       </c>
       <c r="C305" s="2">
         <v>46327</v>
       </c>
       <c r="D305" t="s">
-        <v>310</v>
+        <v>9</v>
       </c>
       <c r="E305" s="3">
         <v>46327</v>
+      </c>
+      <c r="F305" t="s">
+        <v>648</v>
+      </c>
+      <c r="G305">
+        <v>367.42</v>
+      </c>
+      <c r="H305">
+        <v>6.12366666666666</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" t="s">
-        <v>18</v>
+        <v>644</v>
       </c>
       <c r="B306" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="C306" s="2">
         <v>46327</v>
       </c>
       <c r="D306" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E306" s="3">
         <v>46327</v>
       </c>
       <c r="F306" t="s">
-        <v>20</v>
+        <v>650</v>
       </c>
       <c r="G306">
-        <v>181.25</v>
+        <v>342.08</v>
       </c>
       <c r="H306">
-        <v>3.02083333333333</v>
+        <v>5.70133333333333</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" t="s">
-        <v>168</v>
+        <v>651</v>
       </c>
       <c r="B307" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="C307" s="2">
         <v>46327</v>
@@ -11325,21 +11243,21 @@
         <v>46327</v>
       </c>
       <c r="F307" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G307">
-        <v>211.329999999999</v>
+        <v>221.21</v>
       </c>
       <c r="H307">
-        <v>3.52216666666666</v>
+        <v>3.68683333333333</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" t="s">
-        <v>168</v>
+        <v>651</v>
       </c>
       <c r="B308" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="C308" s="2">
         <v>46327</v>
@@ -11351,21 +11269,21 @@
         <v>46327</v>
       </c>
       <c r="F308" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G308">
-        <v>583.67</v>
+        <v>193.71</v>
       </c>
       <c r="H308">
-        <v>9.72783333333333</v>
+        <v>3.2285</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" t="s">
-        <v>168</v>
+        <v>651</v>
       </c>
       <c r="B309" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="C309" s="2">
         <v>46327</v>
@@ -11377,99 +11295,64 @@
         <v>46327</v>
       </c>
       <c r="F309" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="G309">
-        <v>377.88</v>
+        <v>221.25</v>
       </c>
       <c r="H309">
-        <v>6.298</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8">
+        <v>3.6875</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>168</v>
+        <v>658</v>
       </c>
       <c r="B310" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C310" s="2">
         <v>46327</v>
       </c>
       <c r="D310" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E310" s="3">
         <v>46327</v>
-      </c>
-      <c r="F310" t="s">
-        <v>668</v>
-      </c>
-      <c r="G310">
-        <v>173.17</v>
-      </c>
-      <c r="H310">
-        <v>2.88616666666666</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8">
-      <c r="A311" t="s">
-        <v>98</v>
-      </c>
-      <c r="B311" t="s">
-        <v>669</v>
-      </c>
-      <c r="C311" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D311" t="s">
-        <v>9</v>
-      </c>
-      <c r="E311" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F311" t="s">
-        <v>670</v>
-      </c>
-      <c r="G311">
-        <v>263.33</v>
-      </c>
-      <c r="H311">
-        <v>4.38883333333333</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="B312" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="C312" s="2">
         <v>46327</v>
       </c>
       <c r="D312" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E312" s="3">
         <v>46327</v>
       </c>
       <c r="F312" t="s">
-        <v>672</v>
+        <v>20</v>
       </c>
       <c r="G312">
-        <v>277.75</v>
+        <v>181.25</v>
       </c>
       <c r="H312">
-        <v>4.62916666666666</v>
+        <v>3.02083333333333</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
-        <v>673</v>
+        <v>168</v>
       </c>
       <c r="B313" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C313" s="2">
         <v>46327</v>
@@ -11481,21 +11364,21 @@
         <v>46327</v>
       </c>
       <c r="F313" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="G313">
-        <v>348.75</v>
+        <v>211.329999999999</v>
       </c>
       <c r="H313">
-        <v>5.8125</v>
+        <v>3.52216666666666</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" t="s">
-        <v>673</v>
+        <v>168</v>
       </c>
       <c r="B314" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C314" s="2">
         <v>46327</v>
@@ -11507,21 +11390,21 @@
         <v>46327</v>
       </c>
       <c r="F314" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="G314">
-        <v>237.63</v>
+        <v>583.67</v>
       </c>
       <c r="H314">
-        <v>3.9605</v>
+        <v>9.72783333333333</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" t="s">
-        <v>673</v>
+        <v>168</v>
       </c>
       <c r="B315" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C315" s="2">
         <v>46327</v>
@@ -11533,21 +11416,21 @@
         <v>46327</v>
       </c>
       <c r="F315" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="G315">
-        <v>254.25</v>
+        <v>377.88</v>
       </c>
       <c r="H315">
-        <v>4.2375</v>
+        <v>6.298</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" t="s">
-        <v>673</v>
+        <v>168</v>
       </c>
       <c r="B316" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="C316" s="2">
         <v>46327</v>
@@ -11559,21 +11442,21 @@
         <v>46327</v>
       </c>
       <c r="F316" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="G316">
-        <v>214.54</v>
+        <v>173.17</v>
       </c>
       <c r="H316">
-        <v>3.57566666666666</v>
+        <v>2.88616666666666</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
-        <v>673</v>
+        <v>98</v>
       </c>
       <c r="B317" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="C317" s="2">
         <v>46327</v>
@@ -11585,21 +11468,21 @@
         <v>46327</v>
       </c>
       <c r="F317" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="G317">
-        <v>346.75</v>
+        <v>263.33</v>
       </c>
       <c r="H317">
-        <v>5.77916666666666</v>
+        <v>4.38883333333333</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" t="s">
-        <v>673</v>
+        <v>98</v>
       </c>
       <c r="B318" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="C318" s="2">
         <v>46327</v>
@@ -11611,13 +11494,13 @@
         <v>46327</v>
       </c>
       <c r="F318" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="G318">
-        <v>192.88</v>
+        <v>277.75</v>
       </c>
       <c r="H318">
-        <v>3.21466666666666</v>
+        <v>4.62916666666666</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -11625,7 +11508,7 @@
         <v>673</v>
       </c>
       <c r="B319" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="C319" s="2">
         <v>46327</v>
@@ -11637,13 +11520,13 @@
         <v>46327</v>
       </c>
       <c r="F319" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="G319">
-        <v>292.58</v>
+        <v>348.75</v>
       </c>
       <c r="H319">
-        <v>4.87633333333333</v>
+        <v>5.8125</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -11651,7 +11534,7 @@
         <v>673</v>
       </c>
       <c r="B320" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="C320" s="2">
         <v>46327</v>
@@ -11663,13 +11546,13 @@
         <v>46327</v>
       </c>
       <c r="F320" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="G320">
-        <v>282.21</v>
+        <v>237.63</v>
       </c>
       <c r="H320">
-        <v>4.7035</v>
+        <v>3.9605</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -11677,7 +11560,7 @@
         <v>673</v>
       </c>
       <c r="B321" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="C321" s="2">
         <v>46327</v>
@@ -11689,13 +11572,13 @@
         <v>46327</v>
       </c>
       <c r="F321" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="G321">
-        <v>281.88</v>
+        <v>254.25</v>
       </c>
       <c r="H321">
-        <v>4.69799999999999</v>
+        <v>4.2375</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -11703,7 +11586,7 @@
         <v>673</v>
       </c>
       <c r="B322" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="C322" s="2">
         <v>46327</v>
@@ -11715,13 +11598,13 @@
         <v>46327</v>
       </c>
       <c r="F322" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="G322">
-        <v>246.63</v>
+        <v>214.54</v>
       </c>
       <c r="H322">
-        <v>4.1105</v>
+        <v>3.57566666666666</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -11729,7 +11612,7 @@
         <v>673</v>
       </c>
       <c r="B323" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="C323" s="2">
         <v>46327</v>
@@ -11741,13 +11624,13 @@
         <v>46327</v>
       </c>
       <c r="F323" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="G323">
-        <v>406.63</v>
+        <v>346.75</v>
       </c>
       <c r="H323">
-        <v>6.77716666666666</v>
+        <v>5.77916666666666</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -11755,7 +11638,7 @@
         <v>673</v>
       </c>
       <c r="B324" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="C324" s="2">
         <v>46327</v>
@@ -11767,21 +11650,21 @@
         <v>46327</v>
       </c>
       <c r="F324" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="G324">
-        <v>228.42</v>
+        <v>192.88</v>
       </c>
       <c r="H324">
-        <v>3.807</v>
+        <v>3.21466666666666</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="B325" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="C325" s="2">
         <v>46327</v>
@@ -11793,21 +11676,21 @@
         <v>46327</v>
       </c>
       <c r="F325" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="G325">
-        <v>134</v>
+        <v>292.58</v>
       </c>
       <c r="H325">
-        <v>2.23333333333333</v>
+        <v>4.87633333333333</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="B326" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="C326" s="2">
         <v>46327</v>
@@ -11819,21 +11702,21 @@
         <v>46327</v>
       </c>
       <c r="F326" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="G326">
-        <v>152.29</v>
+        <v>282.21</v>
       </c>
       <c r="H326">
-        <v>2.53816666666666</v>
+        <v>4.7035</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" t="s">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="B327" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="C327" s="2">
         <v>46327</v>
@@ -11845,21 +11728,21 @@
         <v>46327</v>
       </c>
       <c r="F327" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="G327">
-        <v>320.46</v>
+        <v>281.88</v>
       </c>
       <c r="H327">
-        <v>5.34099999999999</v>
+        <v>4.69799999999999</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" t="s">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="B328" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="C328" s="2">
         <v>46327</v>
@@ -11871,21 +11754,21 @@
         <v>46327</v>
       </c>
       <c r="F328" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="G328">
-        <v>257.96</v>
+        <v>246.63</v>
       </c>
       <c r="H328">
-        <v>4.29933333333333</v>
+        <v>4.1105</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
       <c r="B329" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="C329" s="2">
         <v>46327</v>
@@ -11897,21 +11780,21 @@
         <v>46327</v>
       </c>
       <c r="F329" t="s">
-        <v>710</v>
+        <v>695</v>
       </c>
       <c r="G329">
-        <v>488.75</v>
+        <v>406.63</v>
       </c>
       <c r="H329">
-        <v>8.14583333333333</v>
+        <v>6.77716666666666</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" t="s">
-        <v>711</v>
+        <v>673</v>
       </c>
       <c r="B330" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="C330" s="2">
         <v>46327</v>
@@ -11923,47 +11806,47 @@
         <v>46327</v>
       </c>
       <c r="F330" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="G330">
-        <v>216.71</v>
+        <v>228.42</v>
       </c>
       <c r="H330">
-        <v>3.61183333333333</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="B331" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="C331" s="2">
         <v>46327</v>
       </c>
       <c r="D331" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E331" s="3">
         <v>46327</v>
       </c>
       <c r="F331" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="G331">
-        <v>384.58</v>
+        <v>134</v>
       </c>
       <c r="H331">
-        <v>6.40966666666666</v>
+        <v>2.23333333333333</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="B332" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="C332" s="2">
         <v>46327</v>
@@ -11975,21 +11858,21 @@
         <v>46327</v>
       </c>
       <c r="F332" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="G332">
-        <v>271.83</v>
+        <v>152.29</v>
       </c>
       <c r="H332">
-        <v>4.5305</v>
+        <v>2.53816666666666</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B333" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="C333" s="2">
         <v>46327</v>
@@ -12001,70 +11884,73 @@
         <v>46327</v>
       </c>
       <c r="F333" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="G333">
-        <v>371.04</v>
+        <v>320.46</v>
       </c>
       <c r="H333">
-        <v>6.184</v>
+        <v>5.34099999999999</v>
       </c>
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="B334" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="C334" s="2">
         <v>46327</v>
       </c>
       <c r="D334" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E334" s="3">
         <v>46327</v>
       </c>
       <c r="F334" t="s">
-        <v>337</v>
+        <v>707</v>
       </c>
       <c r="G334">
-        <v>490.29</v>
+        <v>257.96</v>
       </c>
       <c r="H334">
-        <v>8.1715</v>
+        <v>4.29933333333333</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" t="s">
-        <v>723</v>
-      </c>
-      <c r="B335" s="8" t="s">
-        <v>724</v>
+        <v>708</v>
+      </c>
+      <c r="B335" t="s">
+        <v>709</v>
       </c>
       <c r="C335" s="2">
         <v>46327</v>
       </c>
       <c r="D335" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E335" s="3">
         <v>46327</v>
       </c>
+      <c r="F335" t="s">
+        <v>710</v>
+      </c>
       <c r="G335">
-        <v>226.38</v>
+        <v>488.75</v>
       </c>
       <c r="H335">
-        <v>3.773</v>
+        <v>8.14583333333333</v>
       </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="B336" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="C336" s="2">
         <v>46327</v>
@@ -12076,58 +11962,73 @@
         <v>46327</v>
       </c>
       <c r="F336" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="G336">
-        <v>214.13</v>
+        <v>216.71</v>
       </c>
       <c r="H336">
-        <v>3.56883333333333</v>
+        <v>3.61183333333333</v>
       </c>
     </row>
     <row r="337" spans="1:8">
       <c r="A337" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="B337" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="C337" s="2">
         <v>46327</v>
       </c>
       <c r="D337" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E337" s="3">
         <v>46327</v>
       </c>
       <c r="F337" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="G337">
-        <v>138.17</v>
+        <v>384.58</v>
       </c>
       <c r="H337">
-        <v>2.30283333333333</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
+        <v>6.40966666666666</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
       <c r="A338" t="s">
-        <v>728</v>
+        <v>714</v>
+      </c>
+      <c r="B338" t="s">
+        <v>717</v>
       </c>
       <c r="C338" s="2">
         <v>46327</v>
       </c>
+      <c r="D338" t="s">
+        <v>9</v>
+      </c>
       <c r="E338" s="3">
         <v>46327</v>
+      </c>
+      <c r="F338" t="s">
+        <v>718</v>
+      </c>
+      <c r="G338">
+        <v>271.83</v>
+      </c>
+      <c r="H338">
+        <v>4.5305</v>
       </c>
     </row>
     <row r="339" spans="1:8">
       <c r="A339" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="B339" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="C339" s="2">
         <v>46327</v>
@@ -12139,73 +12040,70 @@
         <v>46327</v>
       </c>
       <c r="F339" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="G339">
-        <v>255.63</v>
+        <v>371.04</v>
       </c>
       <c r="H339">
-        <v>4.26049999999999</v>
+        <v>6.184</v>
       </c>
     </row>
     <row r="340" spans="1:8">
       <c r="A340" t="s">
-        <v>24</v>
+        <v>721</v>
       </c>
       <c r="B340" t="s">
-        <v>594</v>
+        <v>722</v>
       </c>
       <c r="C340" s="2">
         <v>46327</v>
       </c>
       <c r="D340" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E340" s="3">
         <v>46327</v>
       </c>
       <c r="F340" t="s">
-        <v>734</v>
+        <v>337</v>
       </c>
       <c r="G340">
-        <v>254.83</v>
+        <v>490.29</v>
       </c>
       <c r="H340">
-        <v>4.24716666666666</v>
+        <v>8.1715</v>
       </c>
     </row>
     <row r="341" spans="1:8">
       <c r="A341" t="s">
-        <v>24</v>
-      </c>
-      <c r="B341" t="s">
-        <v>735</v>
+        <v>723</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>724</v>
       </c>
       <c r="C341" s="2">
         <v>46327</v>
       </c>
       <c r="D341" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E341" s="3">
         <v>46327</v>
       </c>
-      <c r="F341" t="s">
-        <v>736</v>
-      </c>
       <c r="G341">
-        <v>223.88</v>
+        <v>226.38</v>
       </c>
       <c r="H341">
-        <v>3.73133333333333</v>
+        <v>3.773</v>
       </c>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" t="s">
-        <v>24</v>
+        <v>725</v>
       </c>
       <c r="B342" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="C342" s="2">
         <v>46327</v>
@@ -12217,21 +12115,21 @@
         <v>46327</v>
       </c>
       <c r="F342" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="G342">
-        <v>197.46</v>
+        <v>214.13</v>
       </c>
       <c r="H342">
-        <v>3.291</v>
+        <v>3.56883333333333</v>
       </c>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="B343" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="C343" s="2">
         <v>46327</v>
@@ -12243,47 +12141,32 @@
         <v>46327</v>
       </c>
       <c r="F343" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="G343">
-        <v>256.08</v>
+        <v>138.17</v>
       </c>
       <c r="H343">
-        <v>4.268</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8">
+        <v>2.30283333333333</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
       <c r="A344" t="s">
-        <v>742</v>
-      </c>
-      <c r="B344" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="C344" s="2">
         <v>46327</v>
       </c>
-      <c r="D344" t="s">
-        <v>9</v>
-      </c>
       <c r="E344" s="3">
         <v>46327</v>
-      </c>
-      <c r="F344" t="s">
-        <v>744</v>
-      </c>
-      <c r="G344">
-        <v>234.17</v>
-      </c>
-      <c r="H344">
-        <v>3.90283333333333</v>
       </c>
     </row>
     <row r="345" spans="1:8">
       <c r="A345" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="B345" t="s">
-        <v>227</v>
+        <v>732</v>
       </c>
       <c r="C345" s="2">
         <v>46327</v>
@@ -12295,21 +12178,21 @@
         <v>46327</v>
       </c>
       <c r="F345" t="s">
-        <v>228</v>
+        <v>733</v>
       </c>
       <c r="G345">
-        <v>432.08</v>
+        <v>255.63</v>
       </c>
       <c r="H345">
-        <v>7.20133333333333</v>
+        <v>4.26049999999999</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" t="s">
-        <v>746</v>
+        <v>24</v>
       </c>
       <c r="B346" t="s">
-        <v>747</v>
+        <v>596</v>
       </c>
       <c r="C346" s="2">
         <v>46327</v>
@@ -12321,21 +12204,21 @@
         <v>46327</v>
       </c>
       <c r="F346" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="G346">
-        <v>350.33</v>
+        <v>254.83</v>
       </c>
       <c r="H346">
-        <v>5.83883333333333</v>
+        <v>4.24716666666666</v>
       </c>
     </row>
     <row r="347" spans="1:8">
       <c r="A347" t="s">
-        <v>749</v>
+        <v>24</v>
       </c>
       <c r="B347" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="C347" s="2">
         <v>46327</v>
@@ -12347,21 +12230,21 @@
         <v>46327</v>
       </c>
       <c r="F347" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="G347">
-        <v>215.67</v>
+        <v>223.88</v>
       </c>
       <c r="H347">
-        <v>3.5945</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
+        <v>3.73133333333333</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
       <c r="A348" t="s">
-        <v>752</v>
+        <v>24</v>
       </c>
       <c r="B348" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="C348" s="2">
         <v>46327</v>
@@ -12371,14 +12254,23 @@
       </c>
       <c r="E348" s="3">
         <v>46327</v>
+      </c>
+      <c r="F348" t="s">
+        <v>738</v>
+      </c>
+      <c r="G348">
+        <v>197.46</v>
+      </c>
+      <c r="H348">
+        <v>3.291</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="B349" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="C349" s="2">
         <v>46327</v>
@@ -12390,21 +12282,21 @@
         <v>46327</v>
       </c>
       <c r="F349" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="G349">
-        <v>556.92</v>
+        <v>256.08</v>
       </c>
       <c r="H349">
-        <v>9.282</v>
+        <v>4.268</v>
       </c>
     </row>
     <row r="350" spans="1:8">
       <c r="A350" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="B350" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="C350" s="2">
         <v>46327</v>
@@ -12416,21 +12308,21 @@
         <v>46327</v>
       </c>
       <c r="F350" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="G350">
-        <v>356.46</v>
+        <v>234.17</v>
       </c>
       <c r="H350">
-        <v>5.941</v>
+        <v>3.90283333333333</v>
       </c>
     </row>
     <row r="351" spans="1:8">
       <c r="A351" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="B351" t="s">
-        <v>759</v>
+        <v>227</v>
       </c>
       <c r="C351" s="2">
         <v>46327</v>
@@ -12442,47 +12334,47 @@
         <v>46327</v>
       </c>
       <c r="F351" t="s">
-        <v>760</v>
+        <v>228</v>
       </c>
       <c r="G351">
-        <v>279.17</v>
+        <v>432.08</v>
       </c>
       <c r="H351">
-        <v>4.65283333333333</v>
+        <v>7.20133333333333</v>
       </c>
     </row>
     <row r="352" spans="1:8">
       <c r="A352" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="B352" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="C352" s="2">
         <v>46327</v>
       </c>
       <c r="D352" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E352" s="3">
         <v>46327</v>
       </c>
       <c r="F352" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="G352">
-        <v>256.5</v>
+        <v>350.33</v>
       </c>
       <c r="H352">
-        <v>4.275</v>
+        <v>5.83883333333333</v>
       </c>
     </row>
     <row r="353" spans="1:8">
       <c r="A353" t="s">
-        <v>33</v>
+        <v>749</v>
       </c>
       <c r="B353" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="C353" s="2">
         <v>46327</v>
@@ -12494,21 +12386,21 @@
         <v>46327</v>
       </c>
       <c r="F353" t="s">
-        <v>108</v>
+        <v>751</v>
       </c>
       <c r="G353">
-        <v>204.079999999999</v>
+        <v>215.67</v>
       </c>
       <c r="H353">
-        <v>3.40133333333333</v>
-      </c>
-    </row>
-    <row r="354" spans="1:8">
+        <v>3.5945</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
       <c r="A354" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="B354" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="C354" s="2">
         <v>46327</v>
@@ -12518,23 +12410,14 @@
       </c>
       <c r="E354" s="3">
         <v>46327</v>
-      </c>
-      <c r="F354" t="s">
-        <v>767</v>
-      </c>
-      <c r="G354">
-        <v>212.96</v>
-      </c>
-      <c r="H354">
-        <v>3.54933333333333</v>
       </c>
     </row>
     <row r="355" spans="1:8">
       <c r="A355" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="B355" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="C355" s="2">
         <v>46327</v>
@@ -12546,21 +12429,21 @@
         <v>46327</v>
       </c>
       <c r="F355" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G355">
-        <v>561.25</v>
+        <v>556.92</v>
       </c>
       <c r="H355">
-        <v>9.35416666666666</v>
+        <v>9.282</v>
       </c>
     </row>
     <row r="356" spans="1:8">
       <c r="A356" t="s">
-        <v>771</v>
+        <v>754</v>
       </c>
       <c r="B356" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="C356" s="2">
         <v>46327</v>
@@ -12572,21 +12455,21 @@
         <v>46327</v>
       </c>
       <c r="F356" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="G356">
-        <v>202.25</v>
+        <v>356.46</v>
       </c>
       <c r="H356">
-        <v>3.37083333333333</v>
+        <v>5.941</v>
       </c>
     </row>
     <row r="357" spans="1:8">
       <c r="A357" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="B357" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="C357" s="2">
         <v>46327</v>
@@ -12598,48 +12481,47 @@
         <v>46327</v>
       </c>
       <c r="F357" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="G357">
-        <v>270.63</v>
+        <v>279.17</v>
       </c>
       <c r="H357">
-        <v>4.51049999999999</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9">
+        <v>4.65283333333333</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
       <c r="A358" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="B358" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="C358" s="2">
         <v>46327</v>
       </c>
       <c r="D358" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E358" s="3">
         <v>46327</v>
       </c>
       <c r="F358" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="G358">
-        <v>321.42</v>
+        <v>256.5</v>
       </c>
       <c r="H358">
-        <v>5.357</v>
-      </c>
-      <c r="I358" s="1"/>
+        <v>4.275</v>
+      </c>
     </row>
     <row r="359" spans="1:8">
       <c r="A359" t="s">
-        <v>777</v>
+        <v>33</v>
       </c>
       <c r="B359" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="C359" s="2">
         <v>46327</v>
@@ -12651,21 +12533,21 @@
         <v>46327</v>
       </c>
       <c r="F359" t="s">
-        <v>781</v>
+        <v>108</v>
       </c>
       <c r="G359">
-        <v>393.79</v>
+        <v>204.079999999999</v>
       </c>
       <c r="H359">
-        <v>6.56316666666666</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
+        <v>3.40133333333333</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
       <c r="A360" t="s">
-        <v>782</v>
-      </c>
-      <c r="B360" s="8" t="s">
-        <v>783</v>
+        <v>765</v>
+      </c>
+      <c r="B360" t="s">
+        <v>766</v>
       </c>
       <c r="C360" s="2">
         <v>46327</v>
@@ -12675,14 +12557,23 @@
       </c>
       <c r="E360" s="3">
         <v>46327</v>
+      </c>
+      <c r="F360" t="s">
+        <v>767</v>
+      </c>
+      <c r="G360">
+        <v>212.96</v>
+      </c>
+      <c r="H360">
+        <v>3.54933333333333</v>
       </c>
     </row>
     <row r="361" spans="1:8">
       <c r="A361" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="B361" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="C361" s="2">
         <v>46327</v>
@@ -12694,21 +12585,21 @@
         <v>46327</v>
       </c>
       <c r="F361" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="G361">
-        <v>241.29</v>
+        <v>561.25</v>
       </c>
       <c r="H361">
-        <v>4.0215</v>
+        <v>9.35416666666666</v>
       </c>
     </row>
     <row r="362" spans="1:8">
       <c r="A362" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="B362" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="C362" s="2">
         <v>46327</v>
@@ -12720,21 +12611,21 @@
         <v>46327</v>
       </c>
       <c r="F362" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="G362">
-        <v>146.54</v>
+        <v>202.25</v>
       </c>
       <c r="H362">
-        <v>2.44233333333333</v>
+        <v>3.37083333333333</v>
       </c>
     </row>
     <row r="363" spans="1:8">
       <c r="A363" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="B363" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="C363" s="2">
         <v>46327</v>
@@ -12746,21 +12637,21 @@
         <v>46327</v>
       </c>
       <c r="F363" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="G363">
-        <v>172.46</v>
+        <v>270.63</v>
       </c>
       <c r="H363">
-        <v>2.87433333333333</v>
-      </c>
-    </row>
-    <row r="364" spans="1:8">
+        <v>4.51049999999999</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="B364" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="C364" s="2">
         <v>46327</v>
@@ -12772,21 +12663,22 @@
         <v>46327</v>
       </c>
       <c r="F364" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="G364">
-        <v>167.46</v>
+        <v>321.42</v>
       </c>
       <c r="H364">
-        <v>2.791</v>
-      </c>
+        <v>5.357</v>
+      </c>
+      <c r="I364" s="1"/>
     </row>
     <row r="365" spans="1:8">
       <c r="A365" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="B365" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="C365" s="2">
         <v>46327</v>
@@ -12798,21 +12690,21 @@
         <v>46327</v>
       </c>
       <c r="F365" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="G365">
-        <v>257.46</v>
+        <v>393.79</v>
       </c>
       <c r="H365">
-        <v>4.29099999999999</v>
-      </c>
-    </row>
-    <row r="366" spans="1:8">
+        <v>6.56316666666666</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
       <c r="A366" t="s">
-        <v>791</v>
-      </c>
-      <c r="B366" t="s">
-        <v>796</v>
+        <v>782</v>
+      </c>
+      <c r="B366" s="8" t="s">
+        <v>783</v>
       </c>
       <c r="C366" s="2">
         <v>46327</v>
@@ -12822,23 +12714,14 @@
       </c>
       <c r="E366" s="3">
         <v>46327</v>
-      </c>
-      <c r="F366" t="s">
-        <v>797</v>
-      </c>
-      <c r="G366">
-        <v>179.21</v>
-      </c>
-      <c r="H366">
-        <v>2.98683333333333</v>
       </c>
     </row>
     <row r="367" spans="1:8">
       <c r="A367" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="B367" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="C367" s="2">
         <v>46327</v>
@@ -12850,21 +12733,21 @@
         <v>46327</v>
       </c>
       <c r="F367" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="G367">
-        <v>541.5</v>
+        <v>241.29</v>
       </c>
       <c r="H367">
-        <v>9.025</v>
+        <v>4.0215</v>
       </c>
     </row>
     <row r="368" spans="1:8">
       <c r="A368" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="B368" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="C368" s="2">
         <v>46327</v>
@@ -12876,21 +12759,21 @@
         <v>46327</v>
       </c>
       <c r="F368" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="G368">
-        <v>307.29</v>
+        <v>146.54</v>
       </c>
       <c r="H368">
-        <v>5.1215</v>
+        <v>2.44233333333333</v>
       </c>
     </row>
     <row r="369" spans="1:8">
       <c r="A369" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="B369" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="C369" s="2">
         <v>46327</v>
@@ -12902,21 +12785,21 @@
         <v>46327</v>
       </c>
       <c r="F369" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="G369">
-        <v>193.58</v>
+        <v>172.46</v>
       </c>
       <c r="H369">
-        <v>3.22633333333333</v>
+        <v>2.87433333333333</v>
       </c>
     </row>
     <row r="370" spans="1:8">
       <c r="A370" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="B370" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="C370" s="2">
         <v>46327</v>
@@ -12928,21 +12811,21 @@
         <v>46327</v>
       </c>
       <c r="F370" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="G370">
-        <v>132.33</v>
+        <v>167.46</v>
       </c>
       <c r="H370">
-        <v>2.2055</v>
+        <v>2.791</v>
       </c>
     </row>
     <row r="371" spans="1:8">
       <c r="A371" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="B371" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="C371" s="2">
         <v>46327</v>
@@ -12954,21 +12837,21 @@
         <v>46327</v>
       </c>
       <c r="F371" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="G371">
-        <v>210</v>
+        <v>257.46</v>
       </c>
       <c r="H371">
-        <v>3.5</v>
+        <v>4.29099999999999</v>
       </c>
     </row>
     <row r="372" spans="1:8">
       <c r="A372" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="B372" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
       <c r="C372" s="2">
         <v>46327</v>
@@ -12980,21 +12863,21 @@
         <v>46327</v>
       </c>
       <c r="F372" t="s">
-        <v>355</v>
+        <v>797</v>
       </c>
       <c r="G372">
-        <v>251.67</v>
+        <v>179.21</v>
       </c>
       <c r="H372">
-        <v>4.1945</v>
+        <v>2.98683333333333</v>
       </c>
     </row>
     <row r="373" spans="1:8">
       <c r="A373" t="s">
-        <v>45</v>
+        <v>798</v>
       </c>
       <c r="B373" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="C373" s="2">
         <v>46327</v>
@@ -13006,21 +12889,21 @@
         <v>46327</v>
       </c>
       <c r="F373" t="s">
-        <v>816</v>
+        <v>800</v>
       </c>
       <c r="G373">
-        <v>191.88</v>
+        <v>541.5</v>
       </c>
       <c r="H373">
-        <v>3.198</v>
+        <v>9.025</v>
       </c>
     </row>
     <row r="374" spans="1:8">
       <c r="A374" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="B374" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="C374" s="2">
         <v>46327</v>
@@ -13032,21 +12915,21 @@
         <v>46327</v>
       </c>
       <c r="F374" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="G374">
-        <v>230.829999999999</v>
+        <v>307.29</v>
       </c>
       <c r="H374">
-        <v>3.84716666666666</v>
+        <v>5.1215</v>
       </c>
     </row>
     <row r="375" spans="1:8">
       <c r="A375" t="s">
-        <v>113</v>
+        <v>804</v>
       </c>
       <c r="B375" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C375" s="2">
         <v>46327</v>
@@ -13058,47 +12941,47 @@
         <v>46327</v>
       </c>
       <c r="F375" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G375">
-        <v>213.13</v>
+        <v>193.58</v>
       </c>
       <c r="H375">
-        <v>3.55216666666666</v>
+        <v>3.22633333333333</v>
       </c>
     </row>
     <row r="376" spans="1:8">
       <c r="A376" t="s">
-        <v>113</v>
+        <v>807</v>
       </c>
       <c r="B376" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="C376" s="2">
         <v>46327</v>
       </c>
       <c r="D376" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E376" s="3">
         <v>46327</v>
       </c>
       <c r="F376" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="G376">
-        <v>252.25</v>
+        <v>132.33</v>
       </c>
       <c r="H376">
-        <v>4.20416666666666</v>
+        <v>2.2055</v>
       </c>
     </row>
     <row r="377" spans="1:8">
       <c r="A377" t="s">
-        <v>113</v>
+        <v>810</v>
       </c>
       <c r="B377" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C377" s="2">
         <v>46327</v>
@@ -13110,21 +12993,21 @@
         <v>46327</v>
       </c>
       <c r="F377" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="G377">
-        <v>216.25</v>
+        <v>210</v>
       </c>
       <c r="H377">
-        <v>3.60416666666666</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="378" spans="1:8">
       <c r="A378" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="B378" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="C378" s="2">
         <v>46327</v>
@@ -13136,21 +13019,21 @@
         <v>46327</v>
       </c>
       <c r="F378" t="s">
-        <v>828</v>
+        <v>355</v>
       </c>
       <c r="G378">
-        <v>514.79</v>
+        <v>251.67</v>
       </c>
       <c r="H378">
-        <v>8.57983333333333</v>
+        <v>4.1945</v>
       </c>
     </row>
     <row r="379" spans="1:8">
       <c r="A379" t="s">
-        <v>826</v>
+        <v>45</v>
       </c>
       <c r="B379" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="C379" s="2">
         <v>46327</v>
@@ -13162,21 +13045,21 @@
         <v>46327</v>
       </c>
       <c r="F379" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="G379">
-        <v>485.29</v>
+        <v>191.88</v>
       </c>
       <c r="H379">
-        <v>8.08816666666666</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="380" spans="1:8">
       <c r="A380" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="B380" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="C380" s="2">
         <v>46327</v>
@@ -13188,21 +13071,21 @@
         <v>46327</v>
       </c>
       <c r="F380" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="G380">
-        <v>288.83</v>
+        <v>230.829999999999</v>
       </c>
       <c r="H380">
-        <v>4.81383333333333</v>
+        <v>3.84716666666666</v>
       </c>
     </row>
     <row r="381" spans="1:8">
       <c r="A381" t="s">
-        <v>833</v>
+        <v>113</v>
       </c>
       <c r="B381" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="C381" s="2">
         <v>46327</v>
@@ -13214,47 +13097,47 @@
         <v>46327</v>
       </c>
       <c r="F381" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="G381">
-        <v>246.38</v>
+        <v>213.13</v>
       </c>
       <c r="H381">
-        <v>4.10633333333333</v>
+        <v>3.55216666666666</v>
       </c>
     </row>
     <row r="382" spans="1:8">
       <c r="A382" t="s">
-        <v>833</v>
+        <v>113</v>
       </c>
       <c r="B382" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="C382" s="2">
         <v>46327</v>
       </c>
       <c r="D382" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E382" s="3">
         <v>46327</v>
       </c>
       <c r="F382" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="G382">
-        <v>182.33</v>
+        <v>252.25</v>
       </c>
       <c r="H382">
-        <v>3.03883333333333</v>
+        <v>4.20416666666666</v>
       </c>
     </row>
     <row r="383" spans="1:8">
       <c r="A383" t="s">
-        <v>838</v>
-      </c>
-      <c r="B383" s="8" t="s">
-        <v>839</v>
+        <v>113</v>
+      </c>
+      <c r="B383" t="s">
+        <v>824</v>
       </c>
       <c r="C383" s="2">
         <v>46327</v>
@@ -13265,16 +13148,22 @@
       <c r="E383" s="3">
         <v>46327</v>
       </c>
+      <c r="F383" t="s">
+        <v>825</v>
+      </c>
+      <c r="G383">
+        <v>216.25</v>
+      </c>
       <c r="H383">
-        <v>4.20416666666666</v>
+        <v>3.60416666666666</v>
       </c>
     </row>
     <row r="384" spans="1:8">
       <c r="A384" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="B384" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="C384" s="2">
         <v>46327</v>
@@ -13286,21 +13175,21 @@
         <v>46327</v>
       </c>
       <c r="F384" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="G384">
-        <v>187.25</v>
+        <v>514.79</v>
       </c>
       <c r="H384">
-        <v>3.12083333333333</v>
+        <v>8.57983333333333</v>
       </c>
     </row>
     <row r="385" spans="1:8">
       <c r="A385" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="B385" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="C385" s="2">
         <v>46327</v>
@@ -13312,21 +13201,21 @@
         <v>46327</v>
       </c>
       <c r="F385" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="G385">
-        <v>255.21</v>
+        <v>485.29</v>
       </c>
       <c r="H385">
-        <v>4.2535</v>
+        <v>8.08816666666666</v>
       </c>
     </row>
     <row r="386" spans="1:8">
       <c r="A386" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="B386" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="C386" s="2">
         <v>46327</v>
@@ -13338,21 +13227,21 @@
         <v>46327</v>
       </c>
       <c r="F386" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="G386">
-        <v>138.79</v>
+        <v>288.83</v>
       </c>
       <c r="H386">
-        <v>2.31316666666666</v>
+        <v>4.81383333333333</v>
       </c>
     </row>
     <row r="387" spans="1:8">
       <c r="A387" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="B387" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="C387" s="2">
         <v>46327</v>
@@ -13364,21 +13253,21 @@
         <v>46327</v>
       </c>
       <c r="F387" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="G387">
-        <v>331.5</v>
+        <v>246.38</v>
       </c>
       <c r="H387">
-        <v>5.525</v>
+        <v>4.10633333333333</v>
       </c>
     </row>
     <row r="388" spans="1:8">
       <c r="A388" t="s">
-        <v>311</v>
-      </c>
-      <c r="B388" s="8" t="s">
-        <v>850</v>
+        <v>833</v>
+      </c>
+      <c r="B388" t="s">
+        <v>836</v>
       </c>
       <c r="C388" s="2">
         <v>46327</v>
@@ -13390,21 +13279,21 @@
         <v>46327</v>
       </c>
       <c r="F388" t="s">
-        <v>127</v>
+        <v>837</v>
       </c>
       <c r="G388">
-        <v>242.63</v>
+        <v>182.33</v>
       </c>
       <c r="H388">
-        <v>4.04383333333333</v>
+        <v>3.03883333333333</v>
       </c>
     </row>
     <row r="389" spans="1:8">
       <c r="A389" t="s">
-        <v>851</v>
-      </c>
-      <c r="B389" t="s">
-        <v>852</v>
+        <v>838</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>839</v>
       </c>
       <c r="C389" s="2">
         <v>46327</v>
@@ -13415,22 +13304,16 @@
       <c r="E389" s="3">
         <v>46327</v>
       </c>
-      <c r="F389" t="s">
-        <v>853</v>
-      </c>
-      <c r="G389">
-        <v>157.54</v>
-      </c>
       <c r="H389">
-        <v>2.62566666666666</v>
+        <v>4.20416666666666</v>
       </c>
     </row>
     <row r="390" spans="1:8">
       <c r="A390" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="B390" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="C390" s="2">
         <v>46327</v>
@@ -13442,21 +13325,21 @@
         <v>46327</v>
       </c>
       <c r="F390" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="G390">
-        <v>195.25</v>
+        <v>187.25</v>
       </c>
       <c r="H390">
-        <v>3.25416666666666</v>
+        <v>3.12083333333333</v>
       </c>
     </row>
     <row r="391" spans="1:8">
       <c r="A391" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="B391" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
       <c r="C391" s="2">
         <v>46327</v>
@@ -13468,21 +13351,21 @@
         <v>46327</v>
       </c>
       <c r="F391" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="G391">
-        <v>223.13</v>
+        <v>255.21</v>
       </c>
       <c r="H391">
-        <v>3.71883333333333</v>
+        <v>4.2535</v>
       </c>
     </row>
     <row r="392" spans="1:8">
       <c r="A392" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="B392" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="C392" s="2">
         <v>46327</v>
@@ -13494,21 +13377,21 @@
         <v>46327</v>
       </c>
       <c r="F392" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="G392">
-        <v>205.38</v>
+        <v>138.79</v>
       </c>
       <c r="H392">
-        <v>3.423</v>
+        <v>2.31316666666666</v>
       </c>
     </row>
     <row r="393" spans="1:8">
       <c r="A393" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="B393" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="C393" s="2">
         <v>46327</v>
@@ -13520,21 +13403,21 @@
         <v>46327</v>
       </c>
       <c r="F393" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="G393">
-        <v>231.71</v>
+        <v>331.5</v>
       </c>
       <c r="H393">
-        <v>3.86183333333333</v>
+        <v>5.525</v>
       </c>
     </row>
     <row r="394" spans="1:8">
       <c r="A394" t="s">
-        <v>864</v>
-      </c>
-      <c r="B394" t="s">
-        <v>865</v>
+        <v>311</v>
+      </c>
+      <c r="B394" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="C394" s="2">
         <v>46327</v>
@@ -13546,38 +13429,47 @@
         <v>46327</v>
       </c>
       <c r="F394" t="s">
-        <v>866</v>
+        <v>127</v>
       </c>
       <c r="G394">
-        <v>224.579999999999</v>
+        <v>242.63</v>
       </c>
       <c r="H394">
-        <v>3.743</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5">
+        <v>4.04383333333333</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
       <c r="A395" t="s">
-        <v>867</v>
-      </c>
-      <c r="B395" s="8" t="s">
-        <v>868</v>
+        <v>851</v>
+      </c>
+      <c r="B395" t="s">
+        <v>852</v>
       </c>
       <c r="C395" s="2">
         <v>46327</v>
       </c>
       <c r="D395" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E395" s="3">
         <v>46327</v>
+      </c>
+      <c r="F395" t="s">
+        <v>853</v>
+      </c>
+      <c r="G395">
+        <v>157.54</v>
+      </c>
+      <c r="H395">
+        <v>2.62566666666666</v>
       </c>
     </row>
     <row r="396" spans="1:8">
       <c r="A396" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="B396" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="C396" s="2">
         <v>46327</v>
@@ -13589,21 +13481,21 @@
         <v>46327</v>
       </c>
       <c r="F396" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="G396">
-        <v>230.5</v>
+        <v>195.25</v>
       </c>
       <c r="H396">
-        <v>3.84166666666666</v>
+        <v>3.25416666666666</v>
       </c>
     </row>
     <row r="397" spans="1:8">
       <c r="A397" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="B397" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="C397" s="2">
         <v>46327</v>
@@ -13615,21 +13507,21 @@
         <v>46327</v>
       </c>
       <c r="F397" t="s">
-        <v>874</v>
+        <v>858</v>
       </c>
       <c r="G397">
-        <v>298.71</v>
+        <v>223.13</v>
       </c>
       <c r="H397">
-        <v>4.97849999999999</v>
+        <v>3.71883333333333</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="B398" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="C398" s="2">
         <v>46327</v>
@@ -13641,21 +13533,21 @@
         <v>46327</v>
       </c>
       <c r="F398" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="G398">
-        <v>295.92</v>
+        <v>205.38</v>
       </c>
       <c r="H398">
-        <v>4.932</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="399" spans="1:8">
       <c r="A399" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="B399" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="C399" s="2">
         <v>46327</v>
@@ -13667,21 +13559,21 @@
         <v>46327</v>
       </c>
       <c r="F399" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="G399">
-        <v>303.71</v>
+        <v>231.71</v>
       </c>
       <c r="H399">
-        <v>5.06183333333333</v>
+        <v>3.86183333333333</v>
       </c>
     </row>
     <row r="400" spans="1:8">
       <c r="A400" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="B400" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
       <c r="C400" s="2">
         <v>46327</v>
@@ -13693,47 +13585,38 @@
         <v>46327</v>
       </c>
       <c r="F400" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="G400">
-        <v>250.96</v>
+        <v>224.579999999999</v>
       </c>
       <c r="H400">
-        <v>4.18266666666666</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8">
+        <v>3.743</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
       <c r="A401" t="s">
-        <v>872</v>
-      </c>
-      <c r="B401" t="s">
-        <v>881</v>
+        <v>867</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>868</v>
       </c>
       <c r="C401" s="2">
         <v>46327</v>
       </c>
       <c r="D401" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E401" s="3">
         <v>46327</v>
-      </c>
-      <c r="F401" t="s">
-        <v>882</v>
-      </c>
-      <c r="G401">
-        <v>201.079999999999</v>
-      </c>
-      <c r="H401">
-        <v>3.35133333333333</v>
       </c>
     </row>
     <row r="402" spans="1:8">
       <c r="A402" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B402" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="C402" s="2">
         <v>46327</v>
@@ -13745,21 +13628,21 @@
         <v>46327</v>
       </c>
       <c r="F402" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="G402">
-        <v>335.92</v>
+        <v>230.5</v>
       </c>
       <c r="H402">
-        <v>5.59866666666666</v>
+        <v>3.84166666666666</v>
       </c>
     </row>
     <row r="403" spans="1:8">
       <c r="A403" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="B403" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="C403" s="2">
         <v>46327</v>
@@ -13771,21 +13654,21 @@
         <v>46327</v>
       </c>
       <c r="F403" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="G403">
-        <v>427.17</v>
+        <v>298.71</v>
       </c>
       <c r="H403">
-        <v>7.1195</v>
+        <v>4.97849999999999</v>
       </c>
     </row>
     <row r="404" spans="1:8">
       <c r="A404" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="B404" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
       <c r="C404" s="2">
         <v>46327</v>
@@ -13797,21 +13680,21 @@
         <v>46327</v>
       </c>
       <c r="F404" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="G404">
-        <v>193.71</v>
+        <v>295.92</v>
       </c>
       <c r="H404">
-        <v>3.2285</v>
+        <v>4.932</v>
       </c>
     </row>
     <row r="405" spans="1:8">
       <c r="A405" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="B405" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="C405" s="2">
         <v>46327</v>
@@ -13823,21 +13706,21 @@
         <v>46327</v>
       </c>
       <c r="F405" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="G405">
-        <v>236.829999999999</v>
+        <v>303.71</v>
       </c>
       <c r="H405">
-        <v>3.94716666666666</v>
+        <v>5.06183333333333</v>
       </c>
     </row>
     <row r="406" spans="1:8">
       <c r="A406" t="s">
-        <v>182</v>
+        <v>872</v>
       </c>
       <c r="B406" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="C406" s="2">
         <v>46327</v>
@@ -13849,21 +13732,21 @@
         <v>46327</v>
       </c>
       <c r="F406" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
       <c r="G406">
-        <v>187.25</v>
+        <v>250.96</v>
       </c>
       <c r="H406">
-        <v>3.12083333333333</v>
+        <v>4.18266666666666</v>
       </c>
     </row>
     <row r="407" spans="1:8">
       <c r="A407" t="s">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="B407" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="C407" s="2">
         <v>46327</v>
@@ -13875,21 +13758,21 @@
         <v>46327</v>
       </c>
       <c r="F407" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="G407">
-        <v>308.25</v>
+        <v>201.079999999999</v>
       </c>
       <c r="H407">
-        <v>5.1375</v>
+        <v>3.35133333333333</v>
       </c>
     </row>
     <row r="408" spans="1:8">
       <c r="A408" t="s">
-        <v>899</v>
+        <v>872</v>
       </c>
       <c r="B408" t="s">
-        <v>900</v>
+        <v>883</v>
       </c>
       <c r="C408" s="2">
         <v>46327</v>
@@ -13901,21 +13784,21 @@
         <v>46327</v>
       </c>
       <c r="F408" t="s">
-        <v>901</v>
+        <v>884</v>
       </c>
       <c r="G408">
-        <v>254.29</v>
+        <v>335.92</v>
       </c>
       <c r="H408">
-        <v>4.23816666666666</v>
+        <v>5.59866666666666</v>
       </c>
     </row>
     <row r="409" spans="1:8">
       <c r="A409" t="s">
-        <v>902</v>
+        <v>885</v>
       </c>
       <c r="B409" t="s">
-        <v>903</v>
+        <v>886</v>
       </c>
       <c r="C409" s="2">
         <v>46327</v>
@@ -13927,21 +13810,21 @@
         <v>46327</v>
       </c>
       <c r="F409" t="s">
-        <v>904</v>
+        <v>887</v>
       </c>
       <c r="G409">
-        <v>173.5</v>
+        <v>427.17</v>
       </c>
       <c r="H409">
-        <v>2.89166666666666</v>
+        <v>7.1195</v>
       </c>
     </row>
     <row r="410" spans="1:8">
       <c r="A410" t="s">
-        <v>905</v>
+        <v>888</v>
       </c>
       <c r="B410" t="s">
-        <v>906</v>
+        <v>889</v>
       </c>
       <c r="C410" s="2">
         <v>46327</v>
@@ -13953,47 +13836,47 @@
         <v>46327</v>
       </c>
       <c r="F410" t="s">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="G410">
-        <v>336.67</v>
+        <v>193.71</v>
       </c>
       <c r="H410">
-        <v>5.61116666666666</v>
+        <v>3.2285</v>
       </c>
     </row>
     <row r="411" spans="1:8">
       <c r="A411" t="s">
-        <v>908</v>
-      </c>
-      <c r="B411" s="8" t="s">
-        <v>766</v>
+        <v>891</v>
+      </c>
+      <c r="B411" t="s">
+        <v>892</v>
       </c>
       <c r="C411" s="2">
         <v>46327</v>
       </c>
       <c r="D411" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E411" s="3">
         <v>46327</v>
       </c>
       <c r="F411" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="G411">
-        <v>275.5</v>
+        <v>236.829999999999</v>
       </c>
       <c r="H411">
-        <v>4.59166666666666</v>
+        <v>3.94716666666666</v>
       </c>
     </row>
     <row r="412" spans="1:8">
       <c r="A412" t="s">
-        <v>257</v>
-      </c>
-      <c r="B412" s="7" t="s">
-        <v>910</v>
+        <v>182</v>
+      </c>
+      <c r="B412" t="s">
+        <v>894</v>
       </c>
       <c r="C412" s="2">
         <v>46327</v>
@@ -14005,21 +13888,21 @@
         <v>46327</v>
       </c>
       <c r="F412" t="s">
-        <v>259</v>
+        <v>895</v>
       </c>
       <c r="G412">
-        <v>229</v>
+        <v>187.25</v>
       </c>
       <c r="H412">
-        <v>3.81666666666666</v>
+        <v>3.12083333333333</v>
       </c>
     </row>
     <row r="413" spans="1:8">
       <c r="A413" t="s">
-        <v>60</v>
+        <v>896</v>
       </c>
       <c r="B413" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
       <c r="C413" s="2">
         <v>46327</v>
@@ -14031,32 +13914,47 @@
         <v>46327</v>
       </c>
       <c r="F413" t="s">
-        <v>912</v>
+        <v>898</v>
       </c>
       <c r="G413">
-        <v>161.79</v>
+        <v>308.25</v>
       </c>
       <c r="H413">
-        <v>2.6965</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5">
+        <v>5.1375</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
       <c r="A414" t="s">
-        <v>913</v>
+        <v>899</v>
+      </c>
+      <c r="B414" t="s">
+        <v>900</v>
       </c>
       <c r="C414" s="2">
         <v>46327</v>
       </c>
+      <c r="D414" t="s">
+        <v>9</v>
+      </c>
       <c r="E414" s="3">
         <v>46327</v>
+      </c>
+      <c r="F414" t="s">
+        <v>901</v>
+      </c>
+      <c r="G414">
+        <v>254.29</v>
+      </c>
+      <c r="H414">
+        <v>4.23816666666666</v>
       </c>
     </row>
     <row r="415" spans="1:8">
       <c r="A415" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="B415" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="C415" s="2">
         <v>46327</v>
@@ -14068,21 +13966,21 @@
         <v>46327</v>
       </c>
       <c r="F415" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="G415">
-        <v>351</v>
+        <v>173.5</v>
       </c>
       <c r="H415">
-        <v>5.85</v>
+        <v>2.89166666666666</v>
       </c>
     </row>
     <row r="416" spans="1:8">
       <c r="A416" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="B416" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="C416" s="2">
         <v>46327</v>
@@ -14094,46 +13992,73 @@
         <v>46327</v>
       </c>
       <c r="F416" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="G416">
-        <v>306.67</v>
+        <v>336.67</v>
       </c>
       <c r="H416">
-        <v>5.11116666666666</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5">
+        <v>5.61116666666666</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
       <c r="A417" t="s">
-        <v>920</v>
+        <v>908</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>766</v>
       </c>
       <c r="C417" s="2">
         <v>46327</v>
       </c>
+      <c r="D417" t="s">
+        <v>16</v>
+      </c>
       <c r="E417" s="3">
         <v>46327</v>
       </c>
-    </row>
-    <row r="418" spans="1:5">
+      <c r="F417" t="s">
+        <v>909</v>
+      </c>
+      <c r="G417">
+        <v>275.5</v>
+      </c>
+      <c r="H417">
+        <v>4.59166666666666</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
       <c r="A418" t="s">
-        <v>150</v>
-      </c>
-      <c r="B418" t="s">
-        <v>921</v>
+        <v>257</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>910</v>
       </c>
       <c r="C418" s="2">
         <v>46327</v>
       </c>
+      <c r="D418" t="s">
+        <v>9</v>
+      </c>
       <c r="E418" s="3">
         <v>46327</v>
+      </c>
+      <c r="F418" t="s">
+        <v>259</v>
+      </c>
+      <c r="G418">
+        <v>229</v>
+      </c>
+      <c r="H418">
+        <v>3.81666666666666</v>
       </c>
     </row>
     <row r="419" spans="1:8">
       <c r="A419" t="s">
-        <v>922</v>
+        <v>60</v>
       </c>
       <c r="B419" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C419" s="2">
         <v>46327</v>
@@ -14145,47 +14070,32 @@
         <v>46327</v>
       </c>
       <c r="F419" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="G419">
-        <v>262.79</v>
+        <v>161.79</v>
       </c>
       <c r="H419">
-        <v>4.37983333333333</v>
-      </c>
-    </row>
-    <row r="420" spans="1:8">
+        <v>2.6965</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
       <c r="A420" t="s">
-        <v>925</v>
-      </c>
-      <c r="B420" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="C420" s="2">
         <v>46327</v>
       </c>
-      <c r="D420" t="s">
-        <v>9</v>
-      </c>
       <c r="E420" s="3">
         <v>46327</v>
       </c>
-      <c r="F420" t="s">
-        <v>927</v>
-      </c>
-      <c r="G420">
-        <v>214.21</v>
-      </c>
-      <c r="H420">
-        <v>3.57016666666666</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5">
+    </row>
+    <row r="421" spans="1:8">
       <c r="A421" t="s">
-        <v>73</v>
+        <v>914</v>
       </c>
       <c r="B421" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="C421" s="2">
         <v>46327</v>
@@ -14196,13 +14106,22 @@
       <c r="E421" s="3">
         <v>46327</v>
       </c>
-    </row>
-    <row r="422" spans="1:5">
+      <c r="F421" t="s">
+        <v>916</v>
+      </c>
+      <c r="G421">
+        <v>351</v>
+      </c>
+      <c r="H421">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8">
       <c r="A422" t="s">
-        <v>73</v>
+        <v>917</v>
       </c>
       <c r="B422" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="C422" s="2">
         <v>46327</v>
@@ -14213,65 +14132,47 @@
       <c r="E422" s="3">
         <v>46327</v>
       </c>
-    </row>
-    <row r="423" spans="1:8">
+      <c r="F422" t="s">
+        <v>919</v>
+      </c>
+      <c r="G422">
+        <v>306.67</v>
+      </c>
+      <c r="H422">
+        <v>5.11116666666666</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
       <c r="A423" t="s">
-        <v>260</v>
-      </c>
-      <c r="B423" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="C423" s="2">
         <v>46327</v>
       </c>
-      <c r="D423" t="s">
-        <v>9</v>
-      </c>
       <c r="E423" s="3">
         <v>46327</v>
       </c>
-      <c r="F423" t="s">
-        <v>931</v>
-      </c>
-      <c r="G423">
-        <v>290.54</v>
-      </c>
-      <c r="H423">
-        <v>4.84233333333333</v>
-      </c>
-    </row>
-    <row r="424" spans="1:8">
+    </row>
+    <row r="424" spans="1:5">
       <c r="A424" t="s">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="B424" t="s">
-        <v>301</v>
+        <v>921</v>
       </c>
       <c r="C424" s="2">
         <v>46327</v>
       </c>
-      <c r="D424" t="s">
-        <v>9</v>
-      </c>
       <c r="E424" s="3">
         <v>46327</v>
-      </c>
-      <c r="F424" t="s">
-        <v>932</v>
-      </c>
-      <c r="G424">
-        <v>280.5</v>
-      </c>
-      <c r="H424">
-        <v>4.675</v>
       </c>
     </row>
     <row r="425" spans="1:8">
       <c r="A425" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="B425" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="C425" s="2">
         <v>46327</v>
@@ -14283,21 +14184,21 @@
         <v>46327</v>
       </c>
       <c r="F425" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="G425">
-        <v>492.46</v>
+        <v>262.79</v>
       </c>
       <c r="H425">
-        <v>8.20766666666666</v>
+        <v>4.37983333333333</v>
       </c>
     </row>
     <row r="426" spans="1:8">
       <c r="A426" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="B426" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="C426" s="2">
         <v>46327</v>
@@ -14309,21 +14210,21 @@
         <v>46327</v>
       </c>
       <c r="F426" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="G426">
-        <v>237.88</v>
+        <v>214.21</v>
       </c>
       <c r="H426">
-        <v>3.96466666666666</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8">
+        <v>3.57016666666666</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
       <c r="A427" t="s">
-        <v>936</v>
+        <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="C427" s="2">
         <v>46327</v>
@@ -14334,22 +14235,13 @@
       <c r="E427" s="3">
         <v>46327</v>
       </c>
-      <c r="F427" t="s">
-        <v>940</v>
-      </c>
-      <c r="G427">
-        <v>279.46</v>
-      </c>
-      <c r="H427">
-        <v>4.65766666666666</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8">
+    </row>
+    <row r="428" spans="1:5">
       <c r="A428" t="s">
-        <v>936</v>
+        <v>73</v>
       </c>
       <c r="B428" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="C428" s="2">
         <v>46327</v>
@@ -14359,23 +14251,14 @@
       </c>
       <c r="E428" s="3">
         <v>46327</v>
-      </c>
-      <c r="F428" t="s">
-        <v>942</v>
-      </c>
-      <c r="G428">
-        <v>166.329999999999</v>
-      </c>
-      <c r="H428">
-        <v>2.77216666666666</v>
       </c>
     </row>
     <row r="429" spans="1:8">
       <c r="A429" t="s">
-        <v>936</v>
+        <v>260</v>
       </c>
       <c r="B429" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="C429" s="2">
         <v>46327</v>
@@ -14387,21 +14270,21 @@
         <v>46327</v>
       </c>
       <c r="F429" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="G429">
-        <v>272.71</v>
+        <v>290.54</v>
       </c>
       <c r="H429">
-        <v>4.54516666666666</v>
+        <v>4.84233333333333</v>
       </c>
     </row>
     <row r="430" spans="1:8">
       <c r="A430" t="s">
-        <v>936</v>
+        <v>260</v>
       </c>
       <c r="B430" t="s">
-        <v>945</v>
+        <v>301</v>
       </c>
       <c r="C430" s="2">
         <v>46327</v>
@@ -14413,21 +14296,21 @@
         <v>46327</v>
       </c>
       <c r="F430" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="G430">
-        <v>182.67</v>
+        <v>280.5</v>
       </c>
       <c r="H430">
-        <v>3.04449999999999</v>
+        <v>4.675</v>
       </c>
     </row>
     <row r="431" spans="1:8">
       <c r="A431" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B431" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="C431" s="2">
         <v>46327</v>
@@ -14439,13 +14322,13 @@
         <v>46327</v>
       </c>
       <c r="F431" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="G431">
-        <v>225.54</v>
+        <v>492.46</v>
       </c>
       <c r="H431">
-        <v>3.759</v>
+        <v>8.20766666666666</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -14453,7 +14336,7 @@
         <v>936</v>
       </c>
       <c r="B432" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="C432" s="2">
         <v>46327</v>
@@ -14465,13 +14348,13 @@
         <v>46327</v>
       </c>
       <c r="F432" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="G432">
-        <v>528.88</v>
+        <v>237.88</v>
       </c>
       <c r="H432">
-        <v>8.81466666666666</v>
+        <v>3.96466666666666</v>
       </c>
     </row>
     <row r="433" spans="1:8">
@@ -14479,7 +14362,7 @@
         <v>936</v>
       </c>
       <c r="B433" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="C433" s="2">
         <v>46327</v>
@@ -14491,13 +14374,13 @@
         <v>46327</v>
       </c>
       <c r="F433" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="G433">
-        <v>340.5</v>
+        <v>279.46</v>
       </c>
       <c r="H433">
-        <v>5.675</v>
+        <v>4.65766666666666</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -14505,7 +14388,7 @@
         <v>936</v>
       </c>
       <c r="B434" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="C434" s="2">
         <v>46327</v>
@@ -14517,21 +14400,21 @@
         <v>46327</v>
       </c>
       <c r="F434" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="G434">
-        <v>268.54</v>
+        <v>166.329999999999</v>
       </c>
       <c r="H434">
-        <v>4.47566666666666</v>
+        <v>2.77216666666666</v>
       </c>
     </row>
     <row r="435" spans="1:8">
       <c r="A435" t="s">
-        <v>68</v>
+        <v>936</v>
       </c>
       <c r="B435" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="C435" s="2">
         <v>46327</v>
@@ -14543,21 +14426,21 @@
         <v>46327</v>
       </c>
       <c r="F435" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="G435">
-        <v>182.46</v>
+        <v>272.71</v>
       </c>
       <c r="H435">
-        <v>3.041</v>
+        <v>4.54516666666666</v>
       </c>
     </row>
     <row r="436" spans="1:8">
       <c r="A436" t="s">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="B436" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="C436" s="2">
         <v>46327</v>
@@ -14569,21 +14452,21 @@
         <v>46327</v>
       </c>
       <c r="F436" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="G436">
-        <v>258.04</v>
+        <v>182.67</v>
       </c>
       <c r="H436">
-        <v>4.30066666666666</v>
+        <v>3.04449999999999</v>
       </c>
     </row>
     <row r="437" spans="1:8">
       <c r="A437" t="s">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="B437" t="s">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="C437" s="2">
         <v>46327</v>
@@ -14595,21 +14478,21 @@
         <v>46327</v>
       </c>
       <c r="F437" t="s">
-        <v>962</v>
+        <v>948</v>
       </c>
       <c r="G437">
-        <v>194.42</v>
+        <v>225.54</v>
       </c>
       <c r="H437">
-        <v>3.24033333333333</v>
+        <v>3.759</v>
       </c>
     </row>
     <row r="438" spans="1:8">
       <c r="A438" t="s">
-        <v>963</v>
+        <v>936</v>
       </c>
       <c r="B438" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
       <c r="C438" s="2">
         <v>46327</v>
@@ -14621,21 +14504,21 @@
         <v>46327</v>
       </c>
       <c r="F438" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="G438">
-        <v>282.83</v>
+        <v>528.88</v>
       </c>
       <c r="H438">
-        <v>4.71383333333333</v>
+        <v>8.81466666666666</v>
       </c>
     </row>
     <row r="439" spans="1:8">
       <c r="A439" t="s">
-        <v>75</v>
+        <v>936</v>
       </c>
       <c r="B439" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="C439" s="2">
         <v>46327</v>
@@ -14647,21 +14530,21 @@
         <v>46327</v>
       </c>
       <c r="F439" t="s">
-        <v>212</v>
+        <v>952</v>
       </c>
       <c r="G439">
-        <v>200.29</v>
+        <v>340.5</v>
       </c>
       <c r="H439">
-        <v>3.33816666666666</v>
+        <v>5.675</v>
       </c>
     </row>
     <row r="440" spans="1:8">
       <c r="A440" t="s">
-        <v>967</v>
+        <v>936</v>
       </c>
       <c r="B440" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="C440" s="2">
         <v>46327</v>
@@ -14673,21 +14556,21 @@
         <v>46327</v>
       </c>
       <c r="F440" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="G440">
-        <v>277.38</v>
+        <v>268.54</v>
       </c>
       <c r="H440">
-        <v>4.623</v>
+        <v>4.47566666666666</v>
       </c>
     </row>
     <row r="441" spans="1:8">
       <c r="A441" t="s">
-        <v>970</v>
+        <v>68</v>
       </c>
       <c r="B441" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="C441" s="2">
         <v>46327</v>
@@ -14699,21 +14582,21 @@
         <v>46327</v>
       </c>
       <c r="F441" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="G441">
-        <v>280.29</v>
+        <v>182.46</v>
       </c>
       <c r="H441">
-        <v>4.6715</v>
+        <v>3.041</v>
       </c>
     </row>
     <row r="442" spans="1:8">
       <c r="A442" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
       <c r="B442" t="s">
-        <v>973</v>
+        <v>958</v>
       </c>
       <c r="C442" s="2">
         <v>46327</v>
@@ -14725,21 +14608,21 @@
         <v>46327</v>
       </c>
       <c r="F442" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="G442">
-        <v>312.38</v>
+        <v>258.04</v>
       </c>
       <c r="H442">
-        <v>5.20633333333333</v>
+        <v>4.30066666666666</v>
       </c>
     </row>
     <row r="443" spans="1:8">
       <c r="A443" t="s">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="B443" t="s">
-        <v>286</v>
+        <v>961</v>
       </c>
       <c r="C443" s="2">
         <v>46327</v>
@@ -14751,21 +14634,21 @@
         <v>46327</v>
       </c>
       <c r="F443" t="s">
-        <v>287</v>
+        <v>962</v>
       </c>
       <c r="G443">
-        <v>239</v>
+        <v>194.42</v>
       </c>
       <c r="H443">
-        <v>3.98333333333333</v>
+        <v>3.24033333333333</v>
       </c>
     </row>
     <row r="444" spans="1:8">
       <c r="A444" t="s">
-        <v>79</v>
+        <v>963</v>
       </c>
       <c r="B444" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="C444" s="2">
         <v>46327</v>
@@ -14777,21 +14660,21 @@
         <v>46327</v>
       </c>
       <c r="F444" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="G444">
-        <v>600.88</v>
+        <v>282.83</v>
       </c>
       <c r="H444">
-        <v>10.0146666666666</v>
+        <v>4.71383333333333</v>
       </c>
     </row>
     <row r="445" spans="1:8">
       <c r="A445" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B445" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="C445" s="2">
         <v>46327</v>
@@ -14803,21 +14686,21 @@
         <v>46327</v>
       </c>
       <c r="F445" t="s">
-        <v>978</v>
+        <v>212</v>
       </c>
       <c r="G445">
-        <v>240.13</v>
+        <v>200.29</v>
       </c>
       <c r="H445">
-        <v>4.00216666666666</v>
+        <v>3.33816666666666</v>
       </c>
     </row>
     <row r="446" spans="1:8">
       <c r="A446" t="s">
-        <v>79</v>
+        <v>967</v>
       </c>
       <c r="B446" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="C446" s="2">
         <v>46327</v>
@@ -14829,21 +14712,21 @@
         <v>46327</v>
       </c>
       <c r="F446" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="G446">
-        <v>240.54</v>
+        <v>277.38</v>
       </c>
       <c r="H446">
-        <v>4.00899999999999</v>
+        <v>4.623</v>
       </c>
     </row>
     <row r="447" spans="1:8">
       <c r="A447" t="s">
-        <v>79</v>
+        <v>970</v>
       </c>
       <c r="B447" t="s">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="C447" s="2">
         <v>46327</v>
@@ -14855,21 +14738,21 @@
         <v>46327</v>
       </c>
       <c r="F447" t="s">
-        <v>982</v>
+        <v>972</v>
       </c>
       <c r="G447">
-        <v>238.29</v>
+        <v>280.29</v>
       </c>
       <c r="H447">
-        <v>3.9715</v>
+        <v>4.6715</v>
       </c>
     </row>
     <row r="448" spans="1:8">
       <c r="A448" t="s">
-        <v>79</v>
+        <v>970</v>
       </c>
       <c r="B448" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="C448" s="2">
         <v>46327</v>
@@ -14881,21 +14764,21 @@
         <v>46327</v>
       </c>
       <c r="F448" t="s">
-        <v>984</v>
+        <v>974</v>
       </c>
       <c r="G448">
-        <v>236.17</v>
+        <v>312.38</v>
       </c>
       <c r="H448">
-        <v>3.93616666666666</v>
+        <v>5.20633333333333</v>
       </c>
     </row>
     <row r="449" spans="1:8">
       <c r="A449" t="s">
-        <v>79</v>
+        <v>970</v>
       </c>
       <c r="B449" t="s">
-        <v>985</v>
+        <v>286</v>
       </c>
       <c r="C449" s="2">
         <v>46327</v>
@@ -14907,13 +14790,13 @@
         <v>46327</v>
       </c>
       <c r="F449" t="s">
-        <v>986</v>
+        <v>287</v>
       </c>
       <c r="G449">
-        <v>258.13</v>
+        <v>239</v>
       </c>
       <c r="H449">
-        <v>4.30216666666666</v>
+        <v>3.98333333333333</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -14921,7 +14804,7 @@
         <v>79</v>
       </c>
       <c r="B450" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="C450" s="2">
         <v>46327</v>
@@ -14933,13 +14816,13 @@
         <v>46327</v>
       </c>
       <c r="F450" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="G450">
-        <v>243.08</v>
+        <v>600.88</v>
       </c>
       <c r="H450">
-        <v>4.05133333333333</v>
+        <v>10.0146666666666</v>
       </c>
     </row>
     <row r="451" spans="1:8">
@@ -14947,7 +14830,7 @@
         <v>79</v>
       </c>
       <c r="B451" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="C451" s="2">
         <v>46327</v>
@@ -14959,13 +14842,13 @@
         <v>46327</v>
       </c>
       <c r="F451" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="G451">
-        <v>226.13</v>
+        <v>240.13</v>
       </c>
       <c r="H451">
-        <v>3.76883333333333</v>
+        <v>4.00216666666666</v>
       </c>
     </row>
     <row r="452" spans="1:8">
@@ -14973,7 +14856,7 @@
         <v>79</v>
       </c>
       <c r="B452" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="C452" s="2">
         <v>46327</v>
@@ -14985,21 +14868,21 @@
         <v>46327</v>
       </c>
       <c r="F452" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="G452">
-        <v>234.75</v>
+        <v>240.54</v>
       </c>
       <c r="H452">
-        <v>3.9125</v>
+        <v>4.00899999999999</v>
       </c>
     </row>
     <row r="453" spans="1:8">
       <c r="A453" t="s">
-        <v>993</v>
+        <v>79</v>
       </c>
       <c r="B453" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="C453" s="2">
         <v>46327</v>
@@ -15011,21 +14894,21 @@
         <v>46327</v>
       </c>
       <c r="F453" t="s">
-        <v>995</v>
+        <v>982</v>
       </c>
       <c r="G453">
-        <v>203.13</v>
+        <v>238.29</v>
       </c>
       <c r="H453">
-        <v>3.3855</v>
+        <v>3.9715</v>
       </c>
     </row>
     <row r="454" spans="1:8">
       <c r="A454" t="s">
-        <v>993</v>
+        <v>79</v>
       </c>
       <c r="B454" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
       <c r="C454" s="2">
         <v>46327</v>
@@ -15037,21 +14920,21 @@
         <v>46327</v>
       </c>
       <c r="F454" t="s">
-        <v>997</v>
+        <v>984</v>
       </c>
       <c r="G454">
-        <v>205</v>
+        <v>236.17</v>
       </c>
       <c r="H454">
-        <v>3.41666666666666</v>
+        <v>3.93616666666666</v>
       </c>
     </row>
     <row r="455" spans="1:8">
       <c r="A455" t="s">
-        <v>998</v>
+        <v>79</v>
       </c>
       <c r="B455" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
       <c r="C455" s="2">
         <v>46327</v>
@@ -15063,21 +14946,21 @@
         <v>46327</v>
       </c>
       <c r="F455" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="G455">
-        <v>273.17</v>
+        <v>258.13</v>
       </c>
       <c r="H455">
-        <v>4.55283333333333</v>
+        <v>4.30216666666666</v>
       </c>
     </row>
     <row r="456" spans="1:8">
       <c r="A456" t="s">
-        <v>1001</v>
+        <v>79</v>
       </c>
       <c r="B456" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="C456" s="2">
         <v>46327</v>
@@ -15089,21 +14972,21 @@
         <v>46327</v>
       </c>
       <c r="F456" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="G456">
-        <v>280.08</v>
+        <v>243.08</v>
       </c>
       <c r="H456">
-        <v>4.668</v>
+        <v>4.05133333333333</v>
       </c>
     </row>
     <row r="457" spans="1:8">
       <c r="A457" t="s">
-        <v>1001</v>
+        <v>79</v>
       </c>
       <c r="B457" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="C457" s="2">
         <v>46327</v>
@@ -15115,21 +14998,21 @@
         <v>46327</v>
       </c>
       <c r="F457" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="G457">
-        <v>292.29</v>
+        <v>226.13</v>
       </c>
       <c r="H457">
-        <v>4.8715</v>
+        <v>3.76883333333333</v>
       </c>
     </row>
     <row r="458" spans="1:8">
       <c r="A458" t="s">
-        <v>1006</v>
+        <v>79</v>
       </c>
       <c r="B458" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="C458" s="2">
         <v>46327</v>
@@ -15141,21 +15024,21 @@
         <v>46327</v>
       </c>
       <c r="F458" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="G458">
-        <v>215.829999999999</v>
+        <v>234.75</v>
       </c>
       <c r="H458">
-        <v>3.59716666666666</v>
+        <v>3.9125</v>
       </c>
     </row>
     <row r="459" spans="1:8">
       <c r="A459" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="B459" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="C459" s="2">
         <v>46327</v>
@@ -15167,21 +15050,21 @@
         <v>46327</v>
       </c>
       <c r="F459" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="G459">
-        <v>203.579999999999</v>
+        <v>203.13</v>
       </c>
       <c r="H459">
-        <v>3.393</v>
+        <v>3.3855</v>
       </c>
     </row>
     <row r="460" spans="1:8">
       <c r="A460" t="s">
-        <v>1011</v>
+        <v>993</v>
       </c>
       <c r="B460" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="C460" s="2">
         <v>46327</v>
@@ -15193,21 +15076,21 @@
         <v>46327</v>
       </c>
       <c r="F460" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="G460">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H460">
-        <v>3.36666666666666</v>
+        <v>3.41666666666666</v>
       </c>
     </row>
     <row r="461" spans="1:8">
       <c r="A461" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="B461" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="C461" s="2">
         <v>46327</v>
@@ -15219,21 +15102,47 @@
         <v>46327</v>
       </c>
       <c r="F461" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="G461">
-        <v>166.329999999999</v>
+        <v>273.17</v>
       </c>
       <c r="H461">
-        <v>2.77216666666666</v>
+        <v>4.55283333333333</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8">
+      <c r="A462" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C462" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D462" t="s">
+        <v>9</v>
+      </c>
+      <c r="E462" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F462" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G462">
+        <v>280.08</v>
+      </c>
+      <c r="H462">
+        <v>4.668</v>
       </c>
     </row>
     <row r="463" spans="1:8">
       <c r="A463" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="B463" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="C463" s="2">
         <v>46327</v>
@@ -15245,21 +15154,21 @@
         <v>46327</v>
       </c>
       <c r="F463" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="G463">
-        <v>254.75</v>
+        <v>292.29</v>
       </c>
       <c r="H463">
-        <v>4.24583333333333</v>
+        <v>4.8715</v>
       </c>
     </row>
     <row r="464" spans="1:8">
       <c r="A464" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="B464" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="C464" s="2">
         <v>46327</v>
@@ -15271,21 +15180,21 @@
         <v>46327</v>
       </c>
       <c r="F464" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="G464">
-        <v>278.5</v>
+        <v>215.829999999999</v>
       </c>
       <c r="H464">
-        <v>4.64166666666666</v>
+        <v>3.59716666666666</v>
       </c>
     </row>
     <row r="465" spans="1:8">
       <c r="A465" t="s">
-        <v>1023</v>
+        <v>1006</v>
       </c>
       <c r="B465" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="C465" s="2">
         <v>46327</v>
@@ -15297,21 +15206,21 @@
         <v>46327</v>
       </c>
       <c r="F465" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="G465">
-        <v>274.08</v>
+        <v>203.579999999999</v>
       </c>
       <c r="H465">
-        <v>4.568</v>
+        <v>3.393</v>
       </c>
     </row>
     <row r="466" spans="1:8">
       <c r="A466" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="B466" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="C466" s="2">
         <v>46327</v>
@@ -15323,248 +15232,378 @@
         <v>46327</v>
       </c>
       <c r="F466" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="G466">
-        <v>237.46</v>
+        <v>202</v>
       </c>
       <c r="H466">
-        <v>3.95766666666666</v>
+        <v>3.36666666666666</v>
       </c>
     </row>
     <row r="467" spans="1:8">
       <c r="A467" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C467" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D467" t="s">
+        <v>9</v>
+      </c>
+      <c r="E467" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F467" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G467">
+        <v>166.329999999999</v>
+      </c>
+      <c r="H467">
+        <v>2.77216666666666</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8">
+      <c r="A469" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C469" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D469" t="s">
+        <v>9</v>
+      </c>
+      <c r="E469" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F469" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G469">
+        <v>254.75</v>
+      </c>
+      <c r="H469">
+        <v>4.24583333333333</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8">
+      <c r="A470" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C470" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D470" t="s">
+        <v>9</v>
+      </c>
+      <c r="E470" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F470" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G470">
+        <v>278.5</v>
+      </c>
+      <c r="H470">
+        <v>4.64166666666666</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8">
+      <c r="A471" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C471" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D471" t="s">
+        <v>9</v>
+      </c>
+      <c r="E471" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F471" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G471">
+        <v>274.08</v>
+      </c>
+      <c r="H471">
+        <v>4.568</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8">
+      <c r="A472" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C472" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D472" t="s">
+        <v>9</v>
+      </c>
+      <c r="E472" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F472" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G472">
+        <v>237.46</v>
+      </c>
+      <c r="H472">
+        <v>3.95766666666666</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8">
+      <c r="A473" t="s">
         <v>1029</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B473" t="s">
         <v>1030</v>
       </c>
-      <c r="C467" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D467" t="s">
-        <v>9</v>
-      </c>
-      <c r="E467" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F467" t="s">
+      <c r="C473" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D473" t="s">
+        <v>9</v>
+      </c>
+      <c r="E473" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F473" t="s">
         <v>1031</v>
       </c>
-      <c r="G467">
+      <c r="G473">
         <v>421.54</v>
       </c>
-      <c r="H467">
+      <c r="H473">
         <v>7.02566666666666</v>
-      </c>
-    </row>
-    <row r="468" spans="1:8">
-      <c r="A468" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B468" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C468" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D468" t="s">
-        <v>9</v>
-      </c>
-      <c r="E468" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F468" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G468">
-        <v>279</v>
-      </c>
-      <c r="H468">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="469" spans="1:5">
-      <c r="A469" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B469" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="C469" s="2">
-        <v>46327</v>
-      </c>
-      <c r="E469" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="470" ht="15.6" spans="1:8">
-      <c r="A470" s="16"/>
-      <c r="B470" s="16" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C470" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D470" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E470" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F470" s="1"/>
-      <c r="G470" s="1"/>
-      <c r="H470" s="1"/>
-    </row>
-    <row r="471" ht="15.6" spans="1:5">
-      <c r="A471" s="10"/>
-      <c r="B471" s="10" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C471" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D471" t="s">
-        <v>9</v>
-      </c>
-      <c r="E471" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="472" ht="15.6" spans="1:8">
-      <c r="A472" s="16"/>
-      <c r="B472" s="16" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C472" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D472" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E472" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F472" s="1"/>
-      <c r="G472" s="1"/>
-      <c r="H472" s="1"/>
-    </row>
-    <row r="473" ht="15.6" spans="1:5">
-      <c r="A473" s="10"/>
-      <c r="B473" s="10" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C473" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D473" t="s">
-        <v>9</v>
-      </c>
-      <c r="E473" s="3">
-        <v>46327</v>
       </c>
     </row>
     <row r="474" spans="1:8">
       <c r="A474" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C474" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D474" t="s">
+        <v>9</v>
+      </c>
+      <c r="E474" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F474" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G474">
+        <v>279</v>
+      </c>
+      <c r="H474">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B475" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C475" s="2">
+        <v>46327</v>
+      </c>
+      <c r="E475" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="476" ht="15.6" spans="1:8">
+      <c r="A476" s="16"/>
+      <c r="B476" s="16" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C476" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E476" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F476" s="1"/>
+      <c r="G476" s="1"/>
+      <c r="H476" s="1"/>
+    </row>
+    <row r="477" ht="15.6" spans="1:5">
+      <c r="A477" s="10"/>
+      <c r="B477" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C477" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D477" t="s">
+        <v>9</v>
+      </c>
+      <c r="E477" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="478" ht="15.6" spans="1:8">
+      <c r="A478" s="16"/>
+      <c r="B478" s="16" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C478" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E478" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F478" s="1"/>
+      <c r="G478" s="1"/>
+      <c r="H478" s="1"/>
+    </row>
+    <row r="479" ht="15.6" spans="1:5">
+      <c r="A479" s="10"/>
+      <c r="B479" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C479" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D479" t="s">
+        <v>9</v>
+      </c>
+      <c r="E479" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8">
+      <c r="A480" t="s">
         <v>698</v>
       </c>
-      <c r="B474" t="s">
+      <c r="B480" t="s">
         <v>1038</v>
       </c>
-      <c r="C474" s="2">
+      <c r="C480" s="2">
         <v>46328</v>
       </c>
-      <c r="D474" t="s">
+      <c r="D480" t="s">
         <v>16</v>
       </c>
-      <c r="E474" s="3">
+      <c r="E480" s="3">
         <v>46328</v>
       </c>
-      <c r="F474" t="s">
+      <c r="F480" t="s">
         <v>1039</v>
       </c>
-      <c r="G474">
+      <c r="G480">
         <v>273.21</v>
       </c>
-      <c r="H474">
+      <c r="H480">
         <v>4.5535</v>
       </c>
     </row>
-    <row r="475" spans="1:8">
-      <c r="A475" t="s">
+    <row r="481" spans="1:8">
+      <c r="A481" t="s">
         <v>303</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B481" t="s">
         <v>1040</v>
       </c>
-      <c r="C475" s="2">
+      <c r="C481" s="2">
         <v>46330</v>
       </c>
-      <c r="D475" t="s">
-        <v>9</v>
-      </c>
-      <c r="E475" s="3">
+      <c r="D481" t="s">
+        <v>9</v>
+      </c>
+      <c r="E481" s="3">
         <v>46330</v>
       </c>
-      <c r="F475" t="s">
+      <c r="F481" t="s">
         <v>1041</v>
       </c>
-      <c r="G475">
+      <c r="G481">
         <v>204.63</v>
       </c>
-      <c r="H475">
+      <c r="H481">
         <v>3.4105</v>
       </c>
     </row>
-    <row r="476" spans="1:8">
-      <c r="A476" t="s">
+    <row r="482" spans="1:8">
+      <c r="A482" t="s">
         <v>1042</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B482" t="s">
         <v>1043</v>
       </c>
-      <c r="C476" s="2">
+      <c r="C482" s="2">
         <v>46331</v>
       </c>
-      <c r="D476" t="s">
-        <v>9</v>
-      </c>
-      <c r="E476" s="3">
+      <c r="D482" t="s">
+        <v>9</v>
+      </c>
+      <c r="E482" s="3">
         <v>46331</v>
       </c>
-      <c r="F476" t="s">
+      <c r="F482" t="s">
         <v>1044</v>
       </c>
-      <c r="G476">
+      <c r="G482">
         <v>188.58</v>
       </c>
-      <c r="H476">
+      <c r="H482">
         <v>3.143</v>
       </c>
     </row>
-    <row r="477" spans="1:8">
-      <c r="A477" t="s">
+    <row r="483" spans="1:8">
+      <c r="A483" t="s">
         <v>1045</v>
       </c>
-      <c r="B477" t="s">
+      <c r="B483" t="s">
         <v>1046</v>
       </c>
-      <c r="C477" s="2">
+      <c r="C483" s="2">
         <v>46335</v>
       </c>
-      <c r="D477" t="s">
-        <v>9</v>
-      </c>
-      <c r="E477" s="3">
+      <c r="D483" t="s">
+        <v>9</v>
+      </c>
+      <c r="E483" s="3">
         <v>46335</v>
       </c>
-      <c r="F477" t="s">
+      <c r="F483" t="s">
         <v>1047</v>
       </c>
-      <c r="G477">
+      <c r="G483">
         <v>164.29</v>
       </c>
-      <c r="H477">
+      <c r="H483">
         <v>2.73816666666666</v>
       </c>
     </row>
